--- a/2026 여름신앙학교 데일리 스케줄(최종).xlsx
+++ b/2026 여름신앙학교 데일리 스케줄(최종).xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\카카오톡 받은 파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4796E0E0-C7E7-4105-B350-5E0275AC3B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F7685F-D2F8-4EAA-8E1F-3159D113FC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="타임테이블" sheetId="1" r:id="rId1"/>
+    <sheet name="교사 비상연락망" sheetId="2" r:id="rId2"/>
+    <sheet name="학생 비상연락망" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="435">
   <si>
     <t>DAY1</t>
   </si>
@@ -103,16 +105,10 @@
     <t>- 12:55</t>
   </si>
   <si>
-    <t>전체 인원 최종 확인</t>
-  </si>
-  <si>
     <t>점심식사 영수증 취합 및 확인</t>
   </si>
   <si>
     <t>차량 복귀 및 담당 조 인원 체크</t>
-  </si>
-  <si>
-    <t>소화시키기</t>
   </si>
   <si>
     <t xml:space="preserve"> - 13:00</t>
@@ -1321,12 +1317,374 @@
     <t>학생 이동 지도 (강당 &gt; 식당)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>이름</t>
+  </si>
+  <si>
+    <t>이름</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>직함</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>세례명</t>
+  </si>
+  <si>
+    <t>세례명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전화번호 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>박수환</t>
+  </si>
+  <si>
+    <t>요셉</t>
+  </si>
+  <si>
+    <t>안성준</t>
+  </si>
+  <si>
+    <t>안드레아</t>
+  </si>
+  <si>
+    <t>최지혜</t>
+  </si>
+  <si>
+    <t>세레나</t>
+  </si>
+  <si>
+    <t>010-3700-7138</t>
+  </si>
+  <si>
+    <t>이준영</t>
+  </si>
+  <si>
+    <t>루아단</t>
+  </si>
+  <si>
+    <t>010-5590-2527</t>
+  </si>
+  <si>
+    <t>문승일</t>
+  </si>
+  <si>
+    <t>다니엘</t>
+  </si>
+  <si>
+    <t>010-8520-3130</t>
+  </si>
+  <si>
+    <t>한다혜</t>
+  </si>
+  <si>
+    <t>루치아</t>
+  </si>
+  <si>
+    <t>010-4993-5897</t>
+  </si>
+  <si>
+    <t>최대호</t>
+  </si>
+  <si>
+    <t>제네시오</t>
+  </si>
+  <si>
+    <t>010-9445-5236</t>
+  </si>
+  <si>
+    <t>봉사자</t>
+  </si>
+  <si>
+    <t>허대통</t>
+  </si>
+  <si>
+    <t>니콜라오</t>
+  </si>
+  <si>
+    <t>010-6234-6741</t>
+  </si>
+  <si>
+    <t>윤진</t>
+  </si>
+  <si>
+    <t>첼리나</t>
+  </si>
+  <si>
+    <t>010-5652-1097</t>
+  </si>
+  <si>
+    <t>010-6825-5453</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학년</t>
+  </si>
+  <si>
+    <t>성별</t>
+  </si>
+  <si>
+    <t>고2</t>
+  </si>
+  <si>
+    <t>윤준우</t>
+  </si>
+  <si>
+    <t>아가토</t>
+  </si>
+  <si>
+    <t>남</t>
+  </si>
+  <si>
+    <t>임세현</t>
+  </si>
+  <si>
+    <t>프란치스코</t>
+  </si>
+  <si>
+    <t>중1</t>
+  </si>
+  <si>
+    <t>문준희</t>
+  </si>
+  <si>
+    <t>빈첸시아</t>
+  </si>
+  <si>
+    <t>여</t>
+  </si>
+  <si>
+    <t>김태휘</t>
+  </si>
+  <si>
+    <t>마티아</t>
+  </si>
+  <si>
+    <t>황재현</t>
+  </si>
+  <si>
+    <t>미카엘</t>
+  </si>
+  <si>
+    <t>신현철</t>
+  </si>
+  <si>
+    <t>예비자</t>
+  </si>
+  <si>
+    <t>신은철</t>
+  </si>
+  <si>
+    <t>황유정</t>
+  </si>
+  <si>
+    <t>미카엘라</t>
+  </si>
+  <si>
+    <t>반이영</t>
+  </si>
+  <si>
+    <t>라파엘라</t>
+  </si>
+  <si>
+    <t>스텔라</t>
+  </si>
+  <si>
+    <t>중2</t>
+  </si>
+  <si>
+    <t>문준수</t>
+  </si>
+  <si>
+    <t>사도요한</t>
+  </si>
+  <si>
+    <t>이지후</t>
+  </si>
+  <si>
+    <t>카를로 아쿠티스</t>
+  </si>
+  <si>
+    <t>서영채</t>
+  </si>
+  <si>
+    <t>베로니카</t>
+  </si>
+  <si>
+    <t>유영준</t>
+  </si>
+  <si>
+    <t>야고보</t>
+  </si>
+  <si>
+    <t>중3</t>
+  </si>
+  <si>
+    <t>이주하</t>
+  </si>
+  <si>
+    <t>마리스텔라</t>
+  </si>
+  <si>
+    <t>한세라</t>
+  </si>
+  <si>
+    <t>세라피나</t>
+  </si>
+  <si>
+    <t>이아임</t>
+  </si>
+  <si>
+    <t>윤별</t>
+  </si>
+  <si>
+    <t>유연우</t>
+  </si>
+  <si>
+    <t>가브리엘라</t>
+  </si>
+  <si>
+    <t>임세진</t>
+  </si>
+  <si>
+    <t>서동률</t>
+  </si>
+  <si>
+    <t>학생 연락처</t>
+  </si>
+  <si>
+    <t>학부모 연락처</t>
+  </si>
+  <si>
+    <t>010-8329-6758</t>
+  </si>
+  <si>
+    <t>010-4977-6758</t>
+  </si>
+  <si>
+    <t>010-3516-4168</t>
+  </si>
+  <si>
+    <t>010-4644-4168</t>
+  </si>
+  <si>
+    <t>010-4298-9780</t>
+  </si>
+  <si>
+    <t>010-3325-9780</t>
+  </si>
+  <si>
+    <t>010-9543-5181</t>
+  </si>
+  <si>
+    <t>010-4489-5181</t>
+  </si>
+  <si>
+    <t>010-2878-7025</t>
+  </si>
+  <si>
+    <t>010-4599-8022</t>
+  </si>
+  <si>
+    <t>0106434-9495</t>
+  </si>
+  <si>
+    <t>010-6235-9486</t>
+  </si>
+  <si>
+    <t>0106434-9486</t>
+  </si>
+  <si>
+    <t>010-9670-2075</t>
+  </si>
+  <si>
+    <t>010-8519-8992</t>
+  </si>
+  <si>
+    <t>010-2265-8992</t>
+  </si>
+  <si>
+    <t>010-2900-9676</t>
+  </si>
+  <si>
+    <t>010-9022-2108</t>
+  </si>
+  <si>
+    <t>010-4595-4510</t>
+  </si>
+  <si>
+    <t>010-5865-7311</t>
+  </si>
+  <si>
+    <t>010-8061-7311</t>
+  </si>
+  <si>
+    <t>010-4823-5016</t>
+  </si>
+  <si>
+    <t>010-3823-5016</t>
+  </si>
+  <si>
+    <t>010-5486-5839</t>
+  </si>
+  <si>
+    <t>010-9793-7172</t>
+  </si>
+  <si>
+    <t>010-4825-5293</t>
+  </si>
+  <si>
+    <t>010-8271-5293</t>
+  </si>
+  <si>
+    <t>010-8581-5725</t>
+  </si>
+  <si>
+    <t>010-9110-5725</t>
+  </si>
+  <si>
+    <t>010-6432-1097</t>
+  </si>
+  <si>
+    <t>010-8981-4418</t>
+  </si>
+  <si>
+    <t>010-7649-9532</t>
+  </si>
+  <si>
+    <t>010-9104-9531</t>
+  </si>
+  <si>
+    <t>010-4544-4168</t>
+  </si>
+  <si>
+    <t>010-8616-2395</t>
+  </si>
+  <si>
+    <t>010-9089-0228</t>
+  </si>
+  <si>
+    <t>전체 인원 최종 확인 (대호, 대통 조 인원체크)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대호조 인원체크</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대통조 인원체크</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1438,8 +1796,21 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1488,8 +1859,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D2E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="55">
+  <borders count="69">
     <border>
       <left/>
       <right/>
@@ -2042,17 +2437,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2153,11 +2537,196 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2353,10 +2922,10 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2368,10 +2937,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2386,113 +2955,167 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2506,106 +3129,127 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2842,48 +3486,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A2" s="132" t="s">
-        <v>180</v>
-      </c>
-      <c r="B2" s="133"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
+      <c r="A2" s="109" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A3" s="5"/>
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="93" t="s">
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="96"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="114"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="6" t="s">
@@ -2922,19 +3566,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G5" s="14"/>
       <c r="H5" s="15"/>
@@ -2943,66 +3587,66 @@
     </row>
     <row r="6" spans="1:10" ht="18" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>178</v>
-      </c>
       <c r="E6" s="21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I6" s="27" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J6" s="27" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="18" customHeight="1">
       <c r="A7" s="23" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G7" s="27" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1">
@@ -3010,92 +3654,92 @@
         <v>15</v>
       </c>
       <c r="B8" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="H8" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>195</v>
-      </c>
       <c r="I8" s="27" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J8" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="18" customHeight="1">
       <c r="A9" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="B9" s="24" t="s">
-        <v>219</v>
-      </c>
       <c r="C9" s="29" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F9" s="24" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>16</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="18" customHeight="1">
       <c r="A10" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="B10" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="C10" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="29" t="s">
-        <v>222</v>
-      </c>
       <c r="D10" s="24" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I10" s="29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J10" s="29" t="s">
         <v>17</v>
@@ -3103,34 +3747,34 @@
     </row>
     <row r="11" spans="1:10" ht="18" customHeight="1">
       <c r="A11" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="18" customHeight="1">
@@ -3138,31 +3782,31 @@
         <v>18</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F12" s="29" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H12" s="29" t="s">
         <v>19</v>
       </c>
       <c r="I12" s="29" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J12" s="29" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="18" customHeight="1">
@@ -3170,28 +3814,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D13" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>201</v>
+      </c>
+      <c r="G13" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="H13" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="I13" s="47" t="s">
         <v>200</v>
-      </c>
-      <c r="F13" s="47" t="s">
-        <v>203</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="H13" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="I13" s="47" t="s">
-        <v>202</v>
       </c>
       <c r="J13" s="29" t="s">
         <v>21</v>
@@ -3202,31 +3846,31 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>308</v>
+        <v>203</v>
+      </c>
+      <c r="D14" s="56" t="s">
+        <v>306</v>
+      </c>
+      <c r="E14" s="56" t="s">
+        <v>306</v>
+      </c>
+      <c r="F14" s="56" t="s">
+        <v>306</v>
+      </c>
+      <c r="G14" s="56" t="s">
+        <v>306</v>
+      </c>
+      <c r="H14" s="56" t="s">
+        <v>306</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J14" s="27" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="18" customHeight="1">
@@ -3239,675 +3883,687 @@
       <c r="C15" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="107" t="s">
-        <v>181</v>
-      </c>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="86" t="s">
+      <c r="D15" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="F15" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="G15" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="I15" s="91"/>
-      <c r="J15" s="92"/>
+      <c r="H15" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="76" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="18" customHeight="1">
       <c r="A16" s="28" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="29" t="s">
+        <v>432</v>
+      </c>
+      <c r="C16" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="D16" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="86" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="92"/>
-      <c r="F16" s="29" t="s">
+      <c r="E16" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" s="29" t="s">
+      <c r="G16" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="58" t="s">
         <v>19</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>30</v>
+        <v>433</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>30</v>
+        <v>434</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1">
       <c r="A17" s="34" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B17" s="53" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="D17" s="53" t="s">
-        <v>182</v>
+        <v>197</v>
+      </c>
+      <c r="D17" s="162" t="s">
+        <v>180</v>
       </c>
       <c r="E17" s="54" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G17" s="54" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H17" s="33" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I17" s="53" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J17" s="54" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1">
       <c r="A18" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E18" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="E18" s="29" t="s">
-        <v>34</v>
-      </c>
       <c r="F18" s="29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H18" s="32" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J18" s="29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="18" customHeight="1">
       <c r="A19" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="F19" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>170</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>171</v>
-      </c>
-      <c r="F19" s="36" t="s">
-        <v>37</v>
-      </c>
       <c r="G19" s="36" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H19" s="36" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="18" customHeight="1">
       <c r="A20" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="D20" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="F20" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="G20" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="H20" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I20" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="J20" s="29" t="s">
         <v>39</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="E20" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="F20" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="G20" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="H20" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="I20" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="J20" s="29" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="18" customHeight="1">
       <c r="A21" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="D21" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="E21" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="F21" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="E21" s="32" t="s">
+      <c r="J21" s="29" t="s">
         <v>45</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="G21" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="H21" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="J21" s="29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="18" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="B22" s="110" t="s">
-        <v>166</v>
-      </c>
-      <c r="C22" s="112" t="s">
-        <v>234</v>
-      </c>
-      <c r="D22" s="101" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="101" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="101" t="s">
-        <v>48</v>
-      </c>
-      <c r="G22" s="110" t="s">
+        <v>229</v>
+      </c>
+      <c r="B22" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="130" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" s="172" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="169" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="166" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="164" t="s">
+        <v>233</v>
+      </c>
+      <c r="H22" s="106" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="57" t="s">
         <v>235</v>
       </c>
-      <c r="H22" s="101" t="s">
-        <v>48</v>
-      </c>
-      <c r="I22" s="57" t="s">
-        <v>237</v>
-      </c>
       <c r="J22" s="57" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="18" customHeight="1">
       <c r="A23" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="B23" s="114"/>
-      <c r="C23" s="113"/>
-      <c r="D23" s="102"/>
-      <c r="E23" s="102"/>
-      <c r="F23" s="102"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="102"/>
-      <c r="I23" s="99" t="s">
         <v>236</v>
       </c>
-      <c r="J23" s="97" t="s">
-        <v>236</v>
+      <c r="B23" s="132"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="170"/>
+      <c r="F23" s="167"/>
+      <c r="G23" s="165"/>
+      <c r="H23" s="138"/>
+      <c r="I23" s="136" t="s">
+        <v>234</v>
+      </c>
+      <c r="J23" s="134" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1">
       <c r="A24" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="B24" s="115"/>
+        <v>231</v>
+      </c>
+      <c r="B24" s="133"/>
       <c r="C24" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="103"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="103"/>
+        <v>47</v>
+      </c>
+      <c r="D24" s="174"/>
+      <c r="E24" s="171"/>
+      <c r="F24" s="168"/>
       <c r="G24" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="H24" s="103"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="98"/>
+        <v>48</v>
+      </c>
+      <c r="H24" s="163"/>
+      <c r="I24" s="137"/>
+      <c r="J24" s="135"/>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1">
       <c r="A25" s="39" t="s">
+        <v>237</v>
+      </c>
+      <c r="B25" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="C25" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="B25" s="55" t="s">
-        <v>240</v>
-      </c>
-      <c r="C25" s="29" t="s">
-        <v>241</v>
-      </c>
       <c r="D25" s="29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G25" s="29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I25" s="29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J25" s="29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="18" customHeight="1">
       <c r="A26" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="C26" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="D26" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="E26" s="61" t="s">
+        <v>243</v>
+      </c>
+      <c r="F26" s="59" t="s">
+        <v>243</v>
+      </c>
+      <c r="G26" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="H26" s="61" t="s">
+        <v>243</v>
+      </c>
+      <c r="I26" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="D26" s="61" t="s">
-        <v>245</v>
-      </c>
-      <c r="E26" s="61" t="s">
-        <v>245</v>
-      </c>
-      <c r="F26" s="59" t="s">
-        <v>245</v>
-      </c>
-      <c r="G26" s="61" t="s">
+      <c r="J26" s="29" t="s">
         <v>244</v>
-      </c>
-      <c r="H26" s="61" t="s">
-        <v>245</v>
-      </c>
-      <c r="I26" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="J26" s="29" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="18" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="110" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="B27" s="97" t="s">
+        <v>50</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D27" s="60" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F27" s="62" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G27" s="62" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H27" s="62" t="s">
-        <v>202</v>
-      </c>
-      <c r="I27" s="110" t="s">
-        <v>247</v>
-      </c>
-      <c r="J27" s="110" t="s">
-        <v>248</v>
+        <v>200</v>
+      </c>
+      <c r="I27" s="97" t="s">
+        <v>245</v>
+      </c>
+      <c r="J27" s="97" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="18" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="111"/>
-      <c r="C28" s="116" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="116" t="s">
-        <v>54</v>
-      </c>
-      <c r="E28" s="116" t="s">
-        <v>54</v>
-      </c>
-      <c r="F28" s="116" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28" s="116" t="s">
-        <v>54</v>
-      </c>
-      <c r="H28" s="116" t="s">
-        <v>54</v>
-      </c>
-      <c r="I28" s="117"/>
-      <c r="J28" s="117"/>
+        <v>51</v>
+      </c>
+      <c r="B28" s="99"/>
+      <c r="C28" s="128" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="128" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="128" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="128" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="128" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" s="128" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" s="98"/>
+      <c r="J28" s="98"/>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B29" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="111"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="111"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="111"/>
+        <v>54</v>
+      </c>
+      <c r="C29" s="99"/>
+      <c r="D29" s="99"/>
+      <c r="E29" s="99"/>
+      <c r="F29" s="99"/>
+      <c r="G29" s="99"/>
+      <c r="H29" s="99"/>
+      <c r="I29" s="99"/>
+      <c r="J29" s="99"/>
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" s="107" t="s">
-        <v>184</v>
-      </c>
-      <c r="C30" s="91"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="91"/>
-      <c r="F30" s="91"/>
-      <c r="G30" s="91"/>
-      <c r="H30" s="91"/>
-      <c r="I30" s="91"/>
-      <c r="J30" s="92"/>
+        <v>55</v>
+      </c>
+      <c r="B30" s="94" t="s">
+        <v>182</v>
+      </c>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="96"/>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1">
       <c r="A31" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="29" t="s">
+      <c r="D31" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="E31" s="29" t="s">
-        <v>61</v>
-      </c>
       <c r="F31" s="29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="I31" s="110" t="s">
-        <v>201</v>
-      </c>
-      <c r="J31" s="110" t="s">
-        <v>201</v>
+        <v>59</v>
+      </c>
+      <c r="I31" s="97" t="s">
+        <v>199</v>
+      </c>
+      <c r="J31" s="97" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="18" customHeight="1">
       <c r="A32" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="60" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" s="60" t="s">
+        <v>200</v>
+      </c>
+      <c r="E32" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="D32" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="E32" s="42" t="s">
-        <v>64</v>
-      </c>
       <c r="F32" s="60" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G32" s="60" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H32" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="I32" s="117"/>
-      <c r="J32" s="117"/>
+        <v>200</v>
+      </c>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1">
       <c r="A33" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="101" t="s">
+        <v>248</v>
+      </c>
+      <c r="D33" s="96"/>
+      <c r="E33" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="36" t="s">
+      <c r="F33" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="118" t="s">
-        <v>250</v>
-      </c>
-      <c r="D33" s="92"/>
-      <c r="E33" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="F33" s="36" t="s">
-        <v>68</v>
-      </c>
       <c r="G33" s="36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H33" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="I33" s="111"/>
-      <c r="J33" s="111"/>
+        <v>66</v>
+      </c>
+      <c r="I33" s="99"/>
+      <c r="J33" s="99"/>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1">
       <c r="A34" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="101" t="s">
+        <v>247</v>
+      </c>
+      <c r="C34" s="95"/>
+      <c r="D34" s="95"/>
+      <c r="E34" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="118" t="s">
-        <v>249</v>
-      </c>
-      <c r="C34" s="91"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="F34" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="91"/>
-      <c r="J34" s="92"/>
+      <c r="F34" s="126" t="s">
+        <v>68</v>
+      </c>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="96"/>
     </row>
     <row r="35" spans="1:10" ht="18" customHeight="1">
       <c r="A35" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="36" t="s">
-        <v>310</v>
-      </c>
-      <c r="C35" s="36" t="s">
+      <c r="F35" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="G35" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="D35" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="E35" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="F35" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="G35" s="43" t="s">
-        <v>75</v>
-      </c>
       <c r="H35" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="I35" s="123" t="s">
-        <v>311</v>
-      </c>
-      <c r="J35" s="92"/>
+        <v>46</v>
+      </c>
+      <c r="I35" s="127" t="s">
+        <v>309</v>
+      </c>
+      <c r="J35" s="96"/>
     </row>
     <row r="36" spans="1:10" ht="18" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="118" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" s="120"/>
-      <c r="D36" s="120"/>
-      <c r="E36" s="120"/>
-      <c r="F36" s="120"/>
-      <c r="G36" s="120"/>
-      <c r="H36" s="120"/>
-      <c r="I36" s="120"/>
-      <c r="J36" s="121"/>
+        <v>74</v>
+      </c>
+      <c r="B36" s="101" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" s="124"/>
+      <c r="D36" s="124"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="124"/>
+      <c r="G36" s="124"/>
+      <c r="H36" s="124"/>
+      <c r="I36" s="124"/>
+      <c r="J36" s="125"/>
     </row>
     <row r="37" spans="1:10" ht="18" customHeight="1">
       <c r="A37" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="44" t="s">
+      <c r="D37" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="44" t="s">
+      <c r="E37" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="E37" s="44" t="s">
-        <v>82</v>
-      </c>
       <c r="F37" s="44" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G37" s="44" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H37" s="44" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I37" s="44" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J37" s="64" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="18" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B38" s="119" t="s">
-        <v>312</v>
-      </c>
-      <c r="C38" s="120"/>
-      <c r="D38" s="120"/>
-      <c r="E38" s="120"/>
-      <c r="F38" s="120"/>
-      <c r="G38" s="120"/>
-      <c r="H38" s="120"/>
-      <c r="I38" s="120"/>
-      <c r="J38" s="121"/>
+        <v>82</v>
+      </c>
+      <c r="B38" s="104" t="s">
+        <v>310</v>
+      </c>
+      <c r="C38" s="124"/>
+      <c r="D38" s="124"/>
+      <c r="E38" s="124"/>
+      <c r="F38" s="124"/>
+      <c r="G38" s="124"/>
+      <c r="H38" s="124"/>
+      <c r="I38" s="124"/>
+      <c r="J38" s="125"/>
     </row>
     <row r="39" spans="1:10" ht="18" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B39" s="107" t="s">
-        <v>185</v>
-      </c>
-      <c r="C39" s="91"/>
-      <c r="D39" s="91"/>
-      <c r="E39" s="91"/>
-      <c r="F39" s="91"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="91"/>
-      <c r="I39" s="91"/>
-      <c r="J39" s="92"/>
+        <v>83</v>
+      </c>
+      <c r="B39" s="94" t="s">
+        <v>183</v>
+      </c>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
+      <c r="F39" s="95"/>
+      <c r="G39" s="95"/>
+      <c r="H39" s="95"/>
+      <c r="I39" s="95"/>
+      <c r="J39" s="96"/>
     </row>
     <row r="40" spans="1:10" ht="36" customHeight="1" thickBot="1">
-      <c r="A40" s="127" t="s">
-        <v>86</v>
-      </c>
-      <c r="B40" s="128"/>
-      <c r="C40" s="128"/>
-      <c r="D40" s="128"/>
-      <c r="E40" s="128"/>
-      <c r="F40" s="128"/>
-      <c r="G40" s="128"/>
-      <c r="H40" s="128"/>
-      <c r="I40" s="128"/>
-      <c r="J40" s="129"/>
+      <c r="A40" s="121" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="122"/>
+      <c r="C40" s="122"/>
+      <c r="D40" s="122"/>
+      <c r="E40" s="122"/>
+      <c r="F40" s="122"/>
+      <c r="G40" s="122"/>
+      <c r="H40" s="122"/>
+      <c r="I40" s="122"/>
+      <c r="J40" s="123"/>
     </row>
     <row r="41" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A41" s="5"/>
-      <c r="B41" s="93" t="s">
+      <c r="B41" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C41" s="94"/>
-      <c r="D41" s="94"/>
-      <c r="E41" s="94"/>
-      <c r="F41" s="95"/>
-      <c r="G41" s="93" t="s">
+      <c r="C41" s="112"/>
+      <c r="D41" s="112"/>
+      <c r="E41" s="112"/>
+      <c r="F41" s="113"/>
+      <c r="G41" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="H41" s="94"/>
-      <c r="I41" s="94"/>
-      <c r="J41" s="96"/>
+      <c r="H41" s="112"/>
+      <c r="I41" s="112"/>
+      <c r="J41" s="114"/>
     </row>
     <row r="42" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A42" s="6" t="s">
@@ -3945,358 +4601,358 @@
       <c r="A43" s="23">
         <v>0.25</v>
       </c>
-      <c r="B43" s="90" t="s">
-        <v>253</v>
-      </c>
-      <c r="C43" s="91"/>
-      <c r="D43" s="91"/>
-      <c r="E43" s="91"/>
-      <c r="F43" s="91"/>
-      <c r="G43" s="91"/>
-      <c r="H43" s="91"/>
-      <c r="I43" s="91"/>
-      <c r="J43" s="92"/>
+      <c r="B43" s="118" t="s">
+        <v>251</v>
+      </c>
+      <c r="C43" s="95"/>
+      <c r="D43" s="95"/>
+      <c r="E43" s="95"/>
+      <c r="F43" s="95"/>
+      <c r="G43" s="95"/>
+      <c r="H43" s="95"/>
+      <c r="I43" s="95"/>
+      <c r="J43" s="96"/>
     </row>
     <row r="44" spans="1:10" ht="16.5" customHeight="1">
       <c r="A44" s="23">
         <v>0.27777777777777779</v>
       </c>
       <c r="B44" s="46" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C44" s="46" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D44" s="46" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E44" s="46" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F44" s="46" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G44" s="46" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H44" s="46" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I44" s="29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J44" s="29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.5" customHeight="1">
       <c r="A45" s="18" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B45" s="46" t="s">
+        <v>253</v>
+      </c>
+      <c r="C45" s="46" t="s">
+        <v>253</v>
+      </c>
+      <c r="D45" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="E45" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="G45" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="C45" s="46" t="s">
-        <v>255</v>
-      </c>
-      <c r="D45" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="E45" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="F45" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="G45" s="29" t="s">
-        <v>257</v>
-      </c>
       <c r="H45" s="46" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I45" s="29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J45" s="29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.5" customHeight="1">
       <c r="A46" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="105" t="s">
+        <v>254</v>
+      </c>
+      <c r="C46" s="95"/>
+      <c r="D46" s="95"/>
+      <c r="E46" s="95"/>
+      <c r="F46" s="96"/>
+      <c r="G46" s="119" t="s">
         <v>93</v>
       </c>
-      <c r="B46" s="124" t="s">
-        <v>256</v>
-      </c>
-      <c r="C46" s="91"/>
-      <c r="D46" s="91"/>
-      <c r="E46" s="91"/>
-      <c r="F46" s="92"/>
-      <c r="G46" s="125" t="s">
-        <v>95</v>
-      </c>
-      <c r="H46" s="92"/>
-      <c r="I46" s="124" t="s">
-        <v>94</v>
-      </c>
-      <c r="J46" s="92"/>
+      <c r="H46" s="96"/>
+      <c r="I46" s="105" t="s">
+        <v>92</v>
+      </c>
+      <c r="J46" s="96"/>
     </row>
     <row r="47" spans="1:10" ht="16.5" customHeight="1">
       <c r="A47" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="B47" s="46" t="s">
+      <c r="D47" s="120" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="46" t="s">
+      <c r="E47" s="95"/>
+      <c r="F47" s="96"/>
+      <c r="G47" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="D47" s="126" t="s">
-        <v>99</v>
-      </c>
-      <c r="E47" s="91"/>
-      <c r="F47" s="92"/>
-      <c r="G47" s="29" t="s">
-        <v>100</v>
-      </c>
       <c r="H47" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="I47" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="J47" s="92"/>
+        <v>98</v>
+      </c>
+      <c r="I47" s="103" t="s">
+        <v>257</v>
+      </c>
+      <c r="J47" s="96"/>
     </row>
     <row r="48" spans="1:10" ht="16.5" customHeight="1">
       <c r="A48" s="18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C48" s="86" t="s">
-        <v>262</v>
-      </c>
-      <c r="D48" s="91"/>
-      <c r="E48" s="92"/>
+        <v>100</v>
+      </c>
+      <c r="C48" s="103" t="s">
+        <v>260</v>
+      </c>
+      <c r="D48" s="95"/>
+      <c r="E48" s="96"/>
       <c r="F48" s="29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H48" s="29" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I48" s="29" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J48" s="29" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.5" customHeight="1">
       <c r="A49" s="18" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C49" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="D49" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="E49" s="41" t="s">
         <v>263</v>
       </c>
-      <c r="D49" s="41" t="s">
+      <c r="F49" s="24" t="s">
         <v>264</v>
       </c>
-      <c r="E49" s="41" t="s">
-        <v>265</v>
-      </c>
-      <c r="F49" s="24" t="s">
+      <c r="G49" s="76" t="s">
         <v>266</v>
       </c>
-      <c r="G49" s="76" t="s">
-        <v>268</v>
-      </c>
       <c r="H49" s="75" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="I49" s="56" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J49" s="72" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="16.5" customHeight="1">
       <c r="A50" s="18" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B50" s="69" t="s">
+        <v>265</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>103</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>103</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>103</v>
+      </c>
+      <c r="G50" s="143" t="s">
+        <v>280</v>
+      </c>
+      <c r="H50" s="144"/>
+      <c r="I50" s="65" t="s">
         <v>267</v>
       </c>
-      <c r="C50" s="88" t="s">
-        <v>105</v>
-      </c>
-      <c r="D50" s="88" t="s">
-        <v>105</v>
-      </c>
-      <c r="E50" s="88" t="s">
-        <v>105</v>
-      </c>
-      <c r="F50" s="88" t="s">
-        <v>105</v>
-      </c>
-      <c r="G50" s="84" t="s">
-        <v>282</v>
-      </c>
-      <c r="H50" s="85"/>
-      <c r="I50" s="65" t="s">
-        <v>269</v>
-      </c>
       <c r="J50" s="66" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="16.5" customHeight="1">
       <c r="A51" s="68" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B51" s="70" t="s">
-        <v>260</v>
-      </c>
-      <c r="C51" s="89"/>
-      <c r="D51" s="89"/>
-      <c r="E51" s="89"/>
-      <c r="F51" s="89"/>
+        <v>258</v>
+      </c>
+      <c r="C51" s="147"/>
+      <c r="D51" s="147"/>
+      <c r="E51" s="147"/>
+      <c r="F51" s="147"/>
       <c r="G51" s="66" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H51" s="66" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I51" s="65" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J51" s="66" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.5" customHeight="1">
       <c r="A52" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="B52" s="135" t="s">
-        <v>187</v>
-      </c>
-      <c r="C52" s="91"/>
-      <c r="D52" s="91"/>
-      <c r="E52" s="91"/>
-      <c r="F52" s="91"/>
-      <c r="G52" s="109"/>
-      <c r="H52" s="91"/>
-      <c r="I52" s="109"/>
-      <c r="J52" s="136"/>
+        <v>104</v>
+      </c>
+      <c r="B52" s="116" t="s">
+        <v>185</v>
+      </c>
+      <c r="C52" s="95"/>
+      <c r="D52" s="95"/>
+      <c r="E52" s="95"/>
+      <c r="F52" s="95"/>
+      <c r="G52" s="102"/>
+      <c r="H52" s="95"/>
+      <c r="I52" s="102"/>
+      <c r="J52" s="117"/>
     </row>
     <row r="53" spans="1:10" ht="16.5" customHeight="1">
       <c r="A53" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="B53" s="36" t="s">
+      <c r="D53" s="115" t="s">
         <v>108</v>
       </c>
-      <c r="C53" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="D53" s="134" t="s">
-        <v>110</v>
-      </c>
-      <c r="E53" s="134" t="s">
-        <v>110</v>
-      </c>
-      <c r="F53" s="134" t="s">
-        <v>110</v>
+      <c r="E53" s="115" t="s">
+        <v>108</v>
+      </c>
+      <c r="F53" s="115" t="s">
+        <v>108</v>
       </c>
       <c r="G53" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="H53" s="134" t="s">
-        <v>110</v>
+        <v>107</v>
+      </c>
+      <c r="H53" s="115" t="s">
+        <v>108</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J53" s="37"/>
     </row>
     <row r="54" spans="1:10" ht="16.5" customHeight="1">
       <c r="A54" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="B54" s="36" t="s">
+      <c r="D54" s="99"/>
+      <c r="E54" s="99"/>
+      <c r="F54" s="99"/>
+      <c r="G54" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="C54" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="D54" s="111"/>
-      <c r="E54" s="111"/>
-      <c r="F54" s="111"/>
-      <c r="G54" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="H54" s="111"/>
+      <c r="H54" s="99"/>
       <c r="I54" s="36" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J54" s="29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.5" customHeight="1">
       <c r="A55" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B55" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="B55" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="C55" s="81" t="s">
-        <v>116</v>
-      </c>
-      <c r="D55" s="81"/>
-      <c r="E55" s="81"/>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="82"/>
-      <c r="I55" s="81"/>
-      <c r="J55" s="83"/>
+      <c r="C55" s="140" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="140"/>
+      <c r="E55" s="140"/>
+      <c r="F55" s="140"/>
+      <c r="G55" s="140"/>
+      <c r="H55" s="141"/>
+      <c r="I55" s="140"/>
+      <c r="J55" s="142"/>
     </row>
     <row r="56" spans="1:10" ht="16.5" customHeight="1">
       <c r="A56" s="23">
         <v>0.625</v>
       </c>
       <c r="B56" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="C56" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="D56" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="E56" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="C56" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="D56" s="41" t="s">
-        <v>118</v>
-      </c>
-      <c r="E56" s="41" t="s">
-        <v>119</v>
-      </c>
       <c r="F56" s="41" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G56" s="50" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H56" s="71" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I56" s="74"/>
       <c r="J56" s="41" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.5" customHeight="1">
@@ -4304,272 +4960,272 @@
         <v>0.65972222222222221</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C57" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="D57" s="36" t="s">
+        <v>278</v>
+      </c>
+      <c r="E57" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="F57" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="G57" s="73" t="s">
         <v>277</v>
       </c>
-      <c r="D57" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="E57" s="41" t="s">
-        <v>118</v>
-      </c>
-      <c r="F57" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="G57" s="73" t="s">
+      <c r="H57" s="73" t="s">
         <v>279</v>
       </c>
-      <c r="H57" s="73" t="s">
-        <v>281</v>
-      </c>
       <c r="I57" s="36" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J57" s="36"/>
     </row>
     <row r="58" spans="1:10" ht="16.5" customHeight="1">
       <c r="A58" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="C58" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D58" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="36" t="s">
+      <c r="E58" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="F58" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="G58" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="H58" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="C58" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="D58" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="E58" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="F58" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="G58" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="H58" s="36" t="s">
-        <v>125</v>
-      </c>
       <c r="I58" s="36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J58" s="36"/>
     </row>
     <row r="59" spans="1:10" ht="16.5" customHeight="1">
       <c r="A59" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="D59" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="B59" s="29" t="s">
+      <c r="E59" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="C59" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="D59" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="E59" s="29" t="s">
-        <v>129</v>
-      </c>
       <c r="F59" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="G59" s="86" t="s">
-        <v>283</v>
-      </c>
-      <c r="H59" s="87"/>
+        <v>126</v>
+      </c>
+      <c r="G59" s="103" t="s">
+        <v>281</v>
+      </c>
+      <c r="H59" s="145"/>
       <c r="I59" s="29" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J59" s="29" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.5">
       <c r="A60" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B60" s="100" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" s="148"/>
+      <c r="D60" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="B60" s="104" t="s">
-        <v>131</v>
-      </c>
-      <c r="C60" s="105"/>
-      <c r="D60" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="E60" s="104" t="s">
-        <v>131</v>
-      </c>
-      <c r="F60" s="91"/>
-      <c r="G60" s="104" t="s">
-        <v>132</v>
-      </c>
-      <c r="H60" s="91"/>
-      <c r="I60" s="104" t="s">
-        <v>131</v>
-      </c>
-      <c r="J60" s="91"/>
+      <c r="E60" s="100" t="s">
+        <v>129</v>
+      </c>
+      <c r="F60" s="95"/>
+      <c r="G60" s="100" t="s">
+        <v>130</v>
+      </c>
+      <c r="H60" s="95"/>
+      <c r="I60" s="100" t="s">
+        <v>129</v>
+      </c>
+      <c r="J60" s="95"/>
     </row>
     <row r="61" spans="1:10" ht="16.5">
       <c r="A61" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="D61" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="B61" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="C61" s="29" t="s">
-        <v>288</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>135</v>
-      </c>
       <c r="E61" s="29" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G61" s="29" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H61" s="29" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I61" s="29" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J61" s="29" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.5" customHeight="1">
       <c r="A62" s="18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B62" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C62" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="E62" s="70" t="s">
+        <v>289</v>
+      </c>
+      <c r="F62" s="70" t="s">
+        <v>289</v>
+      </c>
+      <c r="G62" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="C62" s="47" t="s">
+      <c r="H62" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="D62" s="29" t="s">
-        <v>293</v>
-      </c>
-      <c r="E62" s="70" t="s">
-        <v>291</v>
-      </c>
-      <c r="F62" s="70" t="s">
-        <v>291</v>
-      </c>
-      <c r="G62" s="29" t="s">
-        <v>289</v>
-      </c>
-      <c r="H62" s="29" t="s">
-        <v>289</v>
-      </c>
       <c r="I62" s="77" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J62" s="70" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="18" customHeight="1">
       <c r="A63" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B63" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C63" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="B63" s="44" t="s">
+      <c r="D63" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="C63" s="44" t="s">
+      <c r="E63" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="D63" s="44" t="s">
+      <c r="F63" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="G63" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="H63" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="I63" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="E63" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="F63" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="G63" s="44" t="s">
+      <c r="J63" s="71" t="s">
         <v>81</v>
-      </c>
-      <c r="H63" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="I63" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="J63" s="71" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="18" customHeight="1">
       <c r="A64" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B64" s="108" t="s">
-        <v>313</v>
-      </c>
-      <c r="C64" s="109"/>
-      <c r="D64" s="109"/>
-      <c r="E64" s="109"/>
-      <c r="F64" s="109"/>
-      <c r="G64" s="109"/>
-      <c r="H64" s="109"/>
-      <c r="I64" s="109"/>
-      <c r="J64" s="109"/>
+        <v>82</v>
+      </c>
+      <c r="B64" s="129" t="s">
+        <v>311</v>
+      </c>
+      <c r="C64" s="102"/>
+      <c r="D64" s="102"/>
+      <c r="E64" s="102"/>
+      <c r="F64" s="102"/>
+      <c r="G64" s="102"/>
+      <c r="H64" s="102"/>
+      <c r="I64" s="102"/>
+      <c r="J64" s="102"/>
     </row>
     <row r="65" spans="1:10" ht="18" customHeight="1">
       <c r="A65" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B65" s="107" t="s">
-        <v>185</v>
-      </c>
-      <c r="C65" s="91"/>
-      <c r="D65" s="91"/>
-      <c r="E65" s="91"/>
-      <c r="F65" s="91"/>
-      <c r="G65" s="91"/>
-      <c r="H65" s="91"/>
-      <c r="I65" s="91"/>
-      <c r="J65" s="92"/>
+        <v>83</v>
+      </c>
+      <c r="B65" s="94" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" s="95"/>
+      <c r="D65" s="95"/>
+      <c r="E65" s="95"/>
+      <c r="F65" s="95"/>
+      <c r="G65" s="95"/>
+      <c r="H65" s="95"/>
+      <c r="I65" s="95"/>
+      <c r="J65" s="96"/>
     </row>
     <row r="66" spans="1:10" ht="36" customHeight="1" thickBot="1">
-      <c r="A66" s="106" t="s">
-        <v>136</v>
-      </c>
-      <c r="B66" s="91"/>
-      <c r="C66" s="91"/>
-      <c r="D66" s="91"/>
-      <c r="E66" s="91"/>
-      <c r="F66" s="91"/>
-      <c r="G66" s="91"/>
-      <c r="H66" s="91"/>
-      <c r="I66" s="91"/>
-      <c r="J66" s="92"/>
+      <c r="A66" s="149" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="95"/>
+      <c r="C66" s="95"/>
+      <c r="D66" s="95"/>
+      <c r="E66" s="95"/>
+      <c r="F66" s="95"/>
+      <c r="G66" s="95"/>
+      <c r="H66" s="95"/>
+      <c r="I66" s="95"/>
+      <c r="J66" s="96"/>
     </row>
     <row r="67" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A67" s="5"/>
-      <c r="B67" s="93" t="s">
+      <c r="B67" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C67" s="94"/>
-      <c r="D67" s="94"/>
-      <c r="E67" s="94"/>
-      <c r="F67" s="95"/>
-      <c r="G67" s="93" t="s">
+      <c r="C67" s="112"/>
+      <c r="D67" s="112"/>
+      <c r="E67" s="112"/>
+      <c r="F67" s="113"/>
+      <c r="G67" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="H67" s="94"/>
-      <c r="I67" s="94"/>
-      <c r="J67" s="96"/>
+      <c r="H67" s="112"/>
+      <c r="I67" s="112"/>
+      <c r="J67" s="114"/>
     </row>
     <row r="68" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A68" s="6" t="s">
@@ -4605,69 +5261,69 @@
     </row>
     <row r="69" spans="1:10" ht="16.5" customHeight="1">
       <c r="A69" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B69" s="90" t="s">
-        <v>186</v>
-      </c>
-      <c r="C69" s="91"/>
-      <c r="D69" s="91"/>
-      <c r="E69" s="91"/>
-      <c r="F69" s="91"/>
-      <c r="G69" s="91"/>
-      <c r="H69" s="92"/>
+        <v>135</v>
+      </c>
+      <c r="B69" s="118" t="s">
+        <v>184</v>
+      </c>
+      <c r="C69" s="95"/>
+      <c r="D69" s="95"/>
+      <c r="E69" s="95"/>
+      <c r="F69" s="95"/>
+      <c r="G69" s="95"/>
+      <c r="H69" s="96"/>
       <c r="I69" s="49"/>
       <c r="J69" s="49"/>
     </row>
     <row r="70" spans="1:10" ht="16.5" customHeight="1">
       <c r="A70" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="C70" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="D70" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="E70" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="F70" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="G70" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="H70" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="I70" s="103" t="s">
         <v>138</v>
       </c>
-      <c r="B70" s="46" t="s">
-        <v>139</v>
-      </c>
-      <c r="C70" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="D70" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="E70" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="F70" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="G70" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="H70" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="I70" s="86" t="s">
-        <v>140</v>
-      </c>
-      <c r="J70" s="92"/>
+      <c r="J70" s="96"/>
     </row>
     <row r="71" spans="1:10" ht="16.5">
       <c r="A71" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="B71" s="141" t="s">
-        <v>317</v>
+        <v>88</v>
+      </c>
+      <c r="B71" s="83" t="s">
+        <v>315</v>
       </c>
       <c r="C71" s="46" t="s">
-        <v>317</v>
-      </c>
-      <c r="D71" s="86" t="s">
-        <v>95</v>
-      </c>
-      <c r="E71" s="101"/>
-      <c r="F71" s="141" t="s">
-        <v>317</v>
+        <v>315</v>
+      </c>
+      <c r="D71" s="103" t="s">
+        <v>93</v>
+      </c>
+      <c r="E71" s="106"/>
+      <c r="F71" s="83" t="s">
+        <v>315</v>
       </c>
       <c r="G71" s="46" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H71" s="29"/>
       <c r="I71" s="22"/>
@@ -4675,161 +5331,161 @@
     </row>
     <row r="72" spans="1:10" ht="16.5" customHeight="1">
       <c r="A72" s="68" t="s">
-        <v>141</v>
-      </c>
-      <c r="B72" s="142" t="s">
-        <v>316</v>
-      </c>
-      <c r="C72" s="138" t="s">
-        <v>316</v>
-      </c>
-      <c r="D72" s="143" t="s">
-        <v>317</v>
-      </c>
-      <c r="E72" s="145" t="s">
-        <v>317</v>
-      </c>
-      <c r="F72" s="148" t="s">
-        <v>316</v>
-      </c>
-      <c r="G72" s="147" t="s">
-        <v>316</v>
+        <v>139</v>
+      </c>
+      <c r="B72" s="85" t="s">
+        <v>314</v>
+      </c>
+      <c r="C72" s="87" t="s">
+        <v>314</v>
+      </c>
+      <c r="D72" s="90" t="s">
+        <v>315</v>
+      </c>
+      <c r="E72" s="88" t="s">
+        <v>315</v>
+      </c>
+      <c r="F72" s="92" t="s">
+        <v>314</v>
+      </c>
+      <c r="G72" s="84" t="s">
+        <v>314</v>
       </c>
       <c r="H72" s="76" t="s">
-        <v>316</v>
-      </c>
-      <c r="I72" s="86" t="s">
-        <v>142</v>
-      </c>
-      <c r="J72" s="92"/>
+        <v>314</v>
+      </c>
+      <c r="I72" s="103" t="s">
+        <v>140</v>
+      </c>
+      <c r="J72" s="96"/>
     </row>
     <row r="73" spans="1:10" ht="16.5" customHeight="1">
       <c r="A73" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B73" s="139"/>
-      <c r="C73" s="139"/>
-      <c r="D73" s="144"/>
-      <c r="E73" s="146"/>
-      <c r="F73" s="149"/>
-      <c r="G73" s="140" t="s">
-        <v>318</v>
-      </c>
-      <c r="H73" s="140" t="s">
-        <v>318</v>
+        <v>141</v>
+      </c>
+      <c r="B73" s="86"/>
+      <c r="C73" s="86"/>
+      <c r="D73" s="91"/>
+      <c r="E73" s="89"/>
+      <c r="F73" s="93"/>
+      <c r="G73" s="82" t="s">
+        <v>316</v>
+      </c>
+      <c r="H73" s="82" t="s">
+        <v>316</v>
       </c>
       <c r="I73" s="29"/>
       <c r="J73" s="29"/>
     </row>
     <row r="74" spans="1:10" ht="16.5" customHeight="1">
       <c r="A74" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="B74" s="104" t="s">
-        <v>146</v>
-      </c>
-      <c r="C74" s="91"/>
-      <c r="D74" s="91"/>
-      <c r="E74" s="109"/>
-      <c r="F74" s="109"/>
-      <c r="G74" s="91"/>
-      <c r="H74" s="91"/>
-      <c r="I74" s="91"/>
-      <c r="J74" s="92"/>
+        <v>143</v>
+      </c>
+      <c r="B74" s="100" t="s">
+        <v>144</v>
+      </c>
+      <c r="C74" s="95"/>
+      <c r="D74" s="95"/>
+      <c r="E74" s="102"/>
+      <c r="F74" s="102"/>
+      <c r="G74" s="95"/>
+      <c r="H74" s="95"/>
+      <c r="I74" s="95"/>
+      <c r="J74" s="96"/>
     </row>
     <row r="75" spans="1:10" ht="16.5" customHeight="1">
       <c r="A75" s="18" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B75" s="29" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C75" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="D75" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="E75" s="29" t="s">
         <v>294</v>
       </c>
-      <c r="D75" s="29" t="s">
-        <v>295</v>
-      </c>
-      <c r="E75" s="29" t="s">
-        <v>296</v>
-      </c>
       <c r="F75" s="29" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G75" s="29" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H75" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="I75" s="110" t="s">
-        <v>92</v>
-      </c>
-      <c r="J75" s="110" t="s">
-        <v>92</v>
+        <v>146</v>
+      </c>
+      <c r="I75" s="97" t="s">
+        <v>90</v>
+      </c>
+      <c r="J75" s="97" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.5" customHeight="1">
       <c r="A76" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="B76" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="C76" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="D76" s="101" t="s">
         <v>149</v>
       </c>
-      <c r="B76" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="C76" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="D76" s="118" t="s">
-        <v>151</v>
-      </c>
-      <c r="E76" s="91"/>
-      <c r="F76" s="91"/>
-      <c r="G76" s="91"/>
-      <c r="H76" s="92"/>
-      <c r="I76" s="111"/>
-      <c r="J76" s="111"/>
+      <c r="E76" s="95"/>
+      <c r="F76" s="95"/>
+      <c r="G76" s="95"/>
+      <c r="H76" s="96"/>
+      <c r="I76" s="99"/>
+      <c r="J76" s="99"/>
     </row>
     <row r="77" spans="1:10" ht="16.5" customHeight="1">
       <c r="A77" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="B77" s="104" t="s">
-        <v>153</v>
-      </c>
-      <c r="C77" s="91"/>
-      <c r="D77" s="91"/>
-      <c r="E77" s="91"/>
-      <c r="F77" s="91"/>
-      <c r="G77" s="91"/>
-      <c r="H77" s="91"/>
-      <c r="I77" s="91"/>
-      <c r="J77" s="92"/>
+        <v>150</v>
+      </c>
+      <c r="B77" s="100" t="s">
+        <v>151</v>
+      </c>
+      <c r="C77" s="95"/>
+      <c r="D77" s="95"/>
+      <c r="E77" s="95"/>
+      <c r="F77" s="95"/>
+      <c r="G77" s="95"/>
+      <c r="H77" s="95"/>
+      <c r="I77" s="95"/>
+      <c r="J77" s="96"/>
     </row>
     <row r="78" spans="1:10" ht="16.5" customHeight="1">
       <c r="A78" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="B78" s="86" t="s">
-        <v>154</v>
-      </c>
-      <c r="C78" s="91"/>
-      <c r="D78" s="91"/>
-      <c r="E78" s="91"/>
-      <c r="F78" s="91"/>
-      <c r="G78" s="91"/>
-      <c r="H78" s="91"/>
-      <c r="I78" s="91"/>
-      <c r="J78" s="92"/>
+        <v>295</v>
+      </c>
+      <c r="B78" s="103" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" s="95"/>
+      <c r="D78" s="95"/>
+      <c r="E78" s="95"/>
+      <c r="F78" s="95"/>
+      <c r="G78" s="95"/>
+      <c r="H78" s="95"/>
+      <c r="I78" s="95"/>
+      <c r="J78" s="96"/>
     </row>
     <row r="79" spans="1:10" ht="16.5" customHeight="1">
       <c r="A79" s="18" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B79" s="29" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C79" s="29" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D79" s="45"/>
       <c r="E79" s="45"/>
@@ -4837,53 +5493,53 @@
       <c r="G79" s="45"/>
       <c r="H79" s="63"/>
       <c r="I79" s="63"/>
-      <c r="J79" s="137"/>
+      <c r="J79" s="81"/>
     </row>
     <row r="80" spans="1:10" ht="16.5" customHeight="1">
       <c r="A80" s="23">
         <v>0.45833333333333331</v>
       </c>
       <c r="C80" s="78" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D80" s="67" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E80" s="67" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F80" s="41" t="s">
         <v>19</v>
       </c>
       <c r="G80" s="40" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H80" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="I80" s="119" t="s">
-        <v>155</v>
-      </c>
-      <c r="J80" s="92"/>
+        <v>197</v>
+      </c>
+      <c r="I80" s="104" t="s">
+        <v>153</v>
+      </c>
+      <c r="J80" s="96"/>
     </row>
     <row r="81" spans="1:10" ht="16.5" customHeight="1">
       <c r="A81" s="68" t="s">
-        <v>314</v>
-      </c>
-      <c r="B81" s="80" t="s">
-        <v>299</v>
-      </c>
-      <c r="C81" s="80"/>
-      <c r="D81" s="80"/>
-      <c r="E81" s="80"/>
+        <v>312</v>
+      </c>
+      <c r="B81" s="139" t="s">
+        <v>297</v>
+      </c>
+      <c r="C81" s="139"/>
+      <c r="D81" s="139"/>
+      <c r="E81" s="139"/>
       <c r="F81" s="51" t="s">
+        <v>296</v>
+      </c>
+      <c r="G81" s="79" t="s">
         <v>298</v>
       </c>
-      <c r="G81" s="79" t="s">
-        <v>300</v>
-      </c>
       <c r="H81" s="51" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I81" s="26"/>
       <c r="J81" s="4"/>
@@ -4893,22 +5549,22 @@
         <v>0.56597222222222221</v>
       </c>
       <c r="B82" s="58" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C82" s="58" t="s">
         <v>24</v>
       </c>
       <c r="D82" s="58" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E82" s="58" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F82" s="29" t="s">
         <v>19</v>
       </c>
       <c r="G82" s="58" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H82" s="29" t="s">
         <v>19</v>
@@ -4921,10 +5577,10 @@
         <v>0.56944444444444442</v>
       </c>
       <c r="B83" s="29" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C83" s="37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D83" s="29"/>
       <c r="E83" s="29"/>
@@ -4939,68 +5595,68 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="B84" s="24" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C84" s="76" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D84" s="76" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E84" s="76" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F84" s="29" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G84" s="76" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H84" s="29" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I84" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J84" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.5" customHeight="1">
       <c r="A85" s="18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B85" s="29" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C85" s="58"/>
       <c r="D85" s="29"/>
       <c r="E85" s="29" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F85" s="29"/>
       <c r="G85" s="29"/>
       <c r="H85" s="29"/>
       <c r="I85" s="22"/>
       <c r="J85" s="29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.5" customHeight="1">
       <c r="A86" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B86" s="107" t="s">
-        <v>164</v>
-      </c>
-      <c r="C86" s="91"/>
-      <c r="D86" s="91"/>
-      <c r="E86" s="91"/>
-      <c r="F86" s="91"/>
-      <c r="G86" s="91"/>
-      <c r="H86" s="91"/>
-      <c r="I86" s="91"/>
-      <c r="J86" s="92"/>
+        <v>161</v>
+      </c>
+      <c r="B86" s="94" t="s">
+        <v>162</v>
+      </c>
+      <c r="C86" s="95"/>
+      <c r="D86" s="95"/>
+      <c r="E86" s="95"/>
+      <c r="F86" s="95"/>
+      <c r="G86" s="95"/>
+      <c r="H86" s="95"/>
+      <c r="I86" s="95"/>
+      <c r="J86" s="96"/>
     </row>
     <row r="87" spans="1:10" ht="16.5" customHeight="1">
       <c r="A87" s="1"/>
@@ -8133,25 +8789,51 @@
     <row r="1015" ht="15.75" customHeight="1"/>
     <row r="1016" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="84">
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="B86:J86"/>
-    <mergeCell ref="I27:I29"/>
-    <mergeCell ref="B77:J77"/>
-    <mergeCell ref="D76:H76"/>
-    <mergeCell ref="B74:J74"/>
-    <mergeCell ref="J75:J76"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="B78:J78"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="D71:E71"/>
+  <mergeCells count="81">
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="C55:J55"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="G67:J67"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="B64:J64"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="J27:J29"/>
+    <mergeCell ref="I31:I33"/>
+    <mergeCell ref="J31:J33"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="C33:D33"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="B3:F3"/>
@@ -8168,60 +8850,622 @@
     <mergeCell ref="G46:H46"/>
     <mergeCell ref="D47:F47"/>
     <mergeCell ref="C48:E48"/>
+    <mergeCell ref="B86:J86"/>
+    <mergeCell ref="I27:I29"/>
+    <mergeCell ref="B77:J77"/>
+    <mergeCell ref="D76:H76"/>
+    <mergeCell ref="B74:J74"/>
+    <mergeCell ref="J75:J76"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="B78:J78"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="D71:E71"/>
     <mergeCell ref="A40:J40"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B38:J38"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B64:J64"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="B39:J39"/>
-    <mergeCell ref="J27:J29"/>
-    <mergeCell ref="I31:I33"/>
-    <mergeCell ref="J31:J33"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="C55:J55"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="G67:J67"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="F72:F73"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.2" bottom="0.2" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D698622E-888B-4A7B-B21C-8244401B22E2}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A1" s="80" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" s="80" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1" s="80" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1" s="80" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A2" s="150" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="151" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" s="151" t="s">
+        <v>324</v>
+      </c>
+      <c r="D2" s="151" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A3" s="152" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="153" t="s">
+        <v>325</v>
+      </c>
+      <c r="C3" s="153" t="s">
+        <v>326</v>
+      </c>
+      <c r="D3" s="154"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A4" s="152" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="153" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="153" t="s">
+        <v>328</v>
+      </c>
+      <c r="D4" s="153" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A5" s="152" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="153" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5" s="153" t="s">
+        <v>331</v>
+      </c>
+      <c r="D5" s="153" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A6" s="152" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="153" t="s">
+        <v>333</v>
+      </c>
+      <c r="C6" s="153" t="s">
+        <v>334</v>
+      </c>
+      <c r="D6" s="153" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A7" s="152" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="153" t="s">
+        <v>336</v>
+      </c>
+      <c r="C7" s="153" t="s">
+        <v>337</v>
+      </c>
+      <c r="D7" s="153" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A8" s="152" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="153" t="s">
+        <v>339</v>
+      </c>
+      <c r="C8" s="153" t="s">
+        <v>340</v>
+      </c>
+      <c r="D8" s="153" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A9" s="152" t="s">
+        <v>342</v>
+      </c>
+      <c r="B9" s="153" t="s">
+        <v>343</v>
+      </c>
+      <c r="C9" s="153" t="s">
+        <v>344</v>
+      </c>
+      <c r="D9" s="153" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A10" s="152" t="s">
+        <v>342</v>
+      </c>
+      <c r="B10" s="153" t="s">
+        <v>346</v>
+      </c>
+      <c r="C10" s="153" t="s">
+        <v>347</v>
+      </c>
+      <c r="D10" s="153" t="s">
+        <v>348</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90C2390-EDF1-4364-8397-ED53C979A520}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="161" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1" s="161" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1" s="161" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1" s="161" t="s">
+        <v>351</v>
+      </c>
+      <c r="E1" s="161" t="s">
+        <v>394</v>
+      </c>
+      <c r="F1" s="161" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="155" t="s">
+        <v>352</v>
+      </c>
+      <c r="B2" s="155" t="s">
+        <v>353</v>
+      </c>
+      <c r="C2" s="155" t="s">
+        <v>354</v>
+      </c>
+      <c r="D2" s="155" t="s">
+        <v>355</v>
+      </c>
+      <c r="E2" s="155" t="s">
+        <v>396</v>
+      </c>
+      <c r="F2" s="155" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="155" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" s="156" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" s="155" t="s">
+        <v>357</v>
+      </c>
+      <c r="D3" s="155" t="s">
+        <v>355</v>
+      </c>
+      <c r="E3" s="155" t="s">
+        <v>398</v>
+      </c>
+      <c r="F3" s="155" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="155" t="s">
+        <v>358</v>
+      </c>
+      <c r="B4" s="157" t="s">
+        <v>359</v>
+      </c>
+      <c r="C4" s="155" t="s">
+        <v>360</v>
+      </c>
+      <c r="D4" s="155" t="s">
+        <v>361</v>
+      </c>
+      <c r="E4" s="155" t="s">
+        <v>400</v>
+      </c>
+      <c r="F4" s="155" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="155" t="s">
+        <v>358</v>
+      </c>
+      <c r="B5" s="155" t="s">
+        <v>362</v>
+      </c>
+      <c r="C5" s="155" t="s">
+        <v>363</v>
+      </c>
+      <c r="D5" s="155" t="s">
+        <v>355</v>
+      </c>
+      <c r="E5" s="155" t="s">
+        <v>402</v>
+      </c>
+      <c r="F5" s="155" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="155" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" s="158" t="s">
+        <v>364</v>
+      </c>
+      <c r="C6" s="158" t="s">
+        <v>365</v>
+      </c>
+      <c r="D6" s="155" t="s">
+        <v>355</v>
+      </c>
+      <c r="E6" s="155" t="s">
+        <v>404</v>
+      </c>
+      <c r="F6" s="155" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="155" t="s">
+        <v>358</v>
+      </c>
+      <c r="B7" s="159" t="s">
+        <v>366</v>
+      </c>
+      <c r="C7" s="155" t="s">
+        <v>367</v>
+      </c>
+      <c r="D7" s="155" t="s">
+        <v>355</v>
+      </c>
+      <c r="E7" s="155" t="s">
+        <v>406</v>
+      </c>
+      <c r="F7" s="155" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="155" t="s">
+        <v>358</v>
+      </c>
+      <c r="B8" s="159" t="s">
+        <v>368</v>
+      </c>
+      <c r="C8" s="155" t="s">
+        <v>367</v>
+      </c>
+      <c r="D8" s="155" t="s">
+        <v>355</v>
+      </c>
+      <c r="E8" s="155" t="s">
+        <v>408</v>
+      </c>
+      <c r="F8" s="155" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="155" t="s">
+        <v>358</v>
+      </c>
+      <c r="B9" s="158" t="s">
+        <v>369</v>
+      </c>
+      <c r="C9" s="158" t="s">
+        <v>370</v>
+      </c>
+      <c r="D9" s="155" t="s">
+        <v>361</v>
+      </c>
+      <c r="E9" s="155" t="s">
+        <v>409</v>
+      </c>
+      <c r="F9" s="155" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="155" t="s">
+        <v>358</v>
+      </c>
+      <c r="B10" s="155" t="s">
+        <v>371</v>
+      </c>
+      <c r="C10" s="155" t="s">
+        <v>372</v>
+      </c>
+      <c r="D10" s="155" t="s">
+        <v>361</v>
+      </c>
+      <c r="E10" s="155" t="s">
+        <v>410</v>
+      </c>
+      <c r="F10" s="155" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="155" t="s">
+        <v>374</v>
+      </c>
+      <c r="B11" s="157" t="s">
+        <v>375</v>
+      </c>
+      <c r="C11" s="155" t="s">
+        <v>376</v>
+      </c>
+      <c r="D11" s="155" t="s">
+        <v>355</v>
+      </c>
+      <c r="E11" s="155" t="s">
+        <v>412</v>
+      </c>
+      <c r="F11" s="155" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="155" t="s">
+        <v>374</v>
+      </c>
+      <c r="B12" s="155" t="s">
+        <v>377</v>
+      </c>
+      <c r="C12" s="155" t="s">
+        <v>378</v>
+      </c>
+      <c r="D12" s="155" t="s">
+        <v>355</v>
+      </c>
+      <c r="E12" s="155" t="s">
+        <v>413</v>
+      </c>
+      <c r="F12" s="155" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="155" t="s">
+        <v>374</v>
+      </c>
+      <c r="B13" s="155" t="s">
+        <v>379</v>
+      </c>
+      <c r="C13" s="155" t="s">
+        <v>380</v>
+      </c>
+      <c r="D13" s="155" t="s">
+        <v>361</v>
+      </c>
+      <c r="E13" s="155" t="s">
+        <v>415</v>
+      </c>
+      <c r="F13" s="155" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="155" t="s">
+        <v>374</v>
+      </c>
+      <c r="B14" s="155" t="s">
+        <v>381</v>
+      </c>
+      <c r="C14" s="155" t="s">
+        <v>382</v>
+      </c>
+      <c r="D14" s="155" t="s">
+        <v>355</v>
+      </c>
+      <c r="E14" s="155" t="s">
+        <v>417</v>
+      </c>
+      <c r="F14" s="155" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="155" t="s">
+        <v>383</v>
+      </c>
+      <c r="B15" s="155" t="s">
+        <v>384</v>
+      </c>
+      <c r="C15" s="155" t="s">
+        <v>385</v>
+      </c>
+      <c r="D15" s="155" t="s">
+        <v>361</v>
+      </c>
+      <c r="E15" s="155" t="s">
+        <v>419</v>
+      </c>
+      <c r="F15" s="155" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="155" t="s">
+        <v>383</v>
+      </c>
+      <c r="B16" s="155" t="s">
+        <v>386</v>
+      </c>
+      <c r="C16" s="155" t="s">
+        <v>387</v>
+      </c>
+      <c r="D16" s="155" t="s">
+        <v>361</v>
+      </c>
+      <c r="E16" s="155" t="s">
+        <v>421</v>
+      </c>
+      <c r="F16" s="155" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="155" t="s">
+        <v>383</v>
+      </c>
+      <c r="B17" s="155" t="s">
+        <v>388</v>
+      </c>
+      <c r="C17" s="155" t="s">
+        <v>367</v>
+      </c>
+      <c r="D17" s="155" t="s">
+        <v>361</v>
+      </c>
+      <c r="E17" s="155" t="s">
+        <v>423</v>
+      </c>
+      <c r="F17" s="155" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="155" t="s">
+        <v>383</v>
+      </c>
+      <c r="B18" s="155" t="s">
+        <v>389</v>
+      </c>
+      <c r="C18" s="155" t="s">
+        <v>373</v>
+      </c>
+      <c r="D18" s="155" t="s">
+        <v>361</v>
+      </c>
+      <c r="E18" s="155" t="s">
+        <v>425</v>
+      </c>
+      <c r="F18" s="155" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="155" t="s">
+        <v>383</v>
+      </c>
+      <c r="B19" s="155" t="s">
+        <v>390</v>
+      </c>
+      <c r="C19" s="155" t="s">
+        <v>391</v>
+      </c>
+      <c r="D19" s="155" t="s">
+        <v>361</v>
+      </c>
+      <c r="E19" s="155" t="s">
+        <v>427</v>
+      </c>
+      <c r="F19" s="155" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="155" t="s">
+        <v>383</v>
+      </c>
+      <c r="B20" s="156" t="s">
+        <v>392</v>
+      </c>
+      <c r="C20" s="155" t="s">
+        <v>373</v>
+      </c>
+      <c r="D20" s="155" t="s">
+        <v>361</v>
+      </c>
+      <c r="E20" s="155" t="s">
+        <v>429</v>
+      </c>
+      <c r="F20" s="155" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="155" t="s">
+        <v>358</v>
+      </c>
+      <c r="B21" s="155" t="s">
+        <v>393</v>
+      </c>
+      <c r="C21" s="155" t="s">
+        <v>367</v>
+      </c>
+      <c r="D21" s="155" t="s">
+        <v>355</v>
+      </c>
+      <c r="E21" s="160" t="s">
+        <v>430</v>
+      </c>
+      <c r="F21" s="160" t="s">
+        <v>431</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/2026 여름신앙학교 데일리 스케줄(최종).xlsx
+++ b/2026 여름신앙학교 데일리 스케줄(최종).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\카카오톡 받은 파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F7685F-D2F8-4EAA-8E1F-3159D113FC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDD8EE3-232F-4DEE-AEB4-65E09702F441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="타임테이블" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="436">
   <si>
     <t>DAY1</t>
   </si>
@@ -1677,6 +1677,10 @@
   </si>
   <si>
     <t>대통조 인원체크</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-4203-2677</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2982,6 +2986,249 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3007,249 +3254,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3486,32 +3490,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="152" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="153"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="154" t="s">
         <v>178</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A3" s="5"/>
@@ -3947,7 +3951,7 @@
       <c r="C17" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="162" t="s">
+      <c r="D17" s="97" t="s">
         <v>180</v>
       </c>
       <c r="E17" s="54" t="s">
@@ -4101,25 +4105,25 @@
       <c r="A22" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="B22" s="97" t="s">
+      <c r="B22" s="141" t="s">
         <v>164</v>
       </c>
-      <c r="C22" s="130" t="s">
+      <c r="C22" s="139" t="s">
         <v>232</v>
       </c>
-      <c r="D22" s="172" t="s">
+      <c r="D22" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="169" t="s">
+      <c r="E22" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="166" t="s">
+      <c r="F22" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="164" t="s">
+      <c r="G22" s="137" t="s">
         <v>233</v>
       </c>
-      <c r="H22" s="106" t="s">
+      <c r="H22" s="132" t="s">
         <v>46</v>
       </c>
       <c r="I22" s="57" t="s">
@@ -4133,17 +4137,17 @@
       <c r="A23" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="B23" s="132"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="173"/>
-      <c r="E23" s="170"/>
-      <c r="F23" s="167"/>
-      <c r="G23" s="165"/>
-      <c r="H23" s="138"/>
-      <c r="I23" s="136" t="s">
+      <c r="B23" s="142"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="127"/>
+      <c r="F23" s="130"/>
+      <c r="G23" s="138"/>
+      <c r="H23" s="133"/>
+      <c r="I23" s="121" t="s">
         <v>234</v>
       </c>
-      <c r="J23" s="134" t="s">
+      <c r="J23" s="119" t="s">
         <v>234</v>
       </c>
     </row>
@@ -4151,19 +4155,19 @@
       <c r="A24" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="B24" s="133"/>
+      <c r="B24" s="143"/>
       <c r="C24" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="174"/>
-      <c r="E24" s="171"/>
-      <c r="F24" s="168"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="131"/>
       <c r="G24" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="H24" s="163"/>
-      <c r="I24" s="137"/>
-      <c r="J24" s="135"/>
+      <c r="H24" s="134"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="120"/>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1">
       <c r="A25" s="39" t="s">
@@ -4233,7 +4237,7 @@
       <c r="A27" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="97" t="s">
+      <c r="B27" s="141" t="s">
         <v>50</v>
       </c>
       <c r="C27" s="60" t="s">
@@ -4254,10 +4258,10 @@
       <c r="H27" s="62" t="s">
         <v>200</v>
       </c>
-      <c r="I27" s="97" t="s">
+      <c r="I27" s="141" t="s">
         <v>245</v>
       </c>
-      <c r="J27" s="97" t="s">
+      <c r="J27" s="141" t="s">
         <v>246</v>
       </c>
     </row>
@@ -4265,27 +4269,27 @@
       <c r="A28" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="99"/>
-      <c r="C28" s="128" t="s">
+      <c r="B28" s="144"/>
+      <c r="C28" s="145" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="128" t="s">
+      <c r="D28" s="145" t="s">
         <v>52</v>
       </c>
-      <c r="E28" s="128" t="s">
+      <c r="E28" s="145" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="128" t="s">
+      <c r="F28" s="145" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="128" t="s">
+      <c r="G28" s="145" t="s">
         <v>52</v>
       </c>
-      <c r="H28" s="128" t="s">
+      <c r="H28" s="145" t="s">
         <v>52</v>
       </c>
-      <c r="I28" s="98"/>
-      <c r="J28" s="98"/>
+      <c r="I28" s="146"/>
+      <c r="J28" s="146"/>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1">
       <c r="A29" s="18" t="s">
@@ -4294,30 +4298,30 @@
       <c r="B29" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="99"/>
-      <c r="D29" s="99"/>
-      <c r="E29" s="99"/>
-      <c r="F29" s="99"/>
-      <c r="G29" s="99"/>
-      <c r="H29" s="99"/>
-      <c r="I29" s="99"/>
-      <c r="J29" s="99"/>
+      <c r="C29" s="144"/>
+      <c r="D29" s="144"/>
+      <c r="E29" s="144"/>
+      <c r="F29" s="144"/>
+      <c r="G29" s="144"/>
+      <c r="H29" s="144"/>
+      <c r="I29" s="144"/>
+      <c r="J29" s="144"/>
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1">
       <c r="A30" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="94" t="s">
+      <c r="B30" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="95"/>
-      <c r="I30" s="95"/>
-      <c r="J30" s="96"/>
+      <c r="C30" s="109"/>
+      <c r="D30" s="109"/>
+      <c r="E30" s="109"/>
+      <c r="F30" s="109"/>
+      <c r="G30" s="109"/>
+      <c r="H30" s="109"/>
+      <c r="I30" s="109"/>
+      <c r="J30" s="110"/>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1">
       <c r="A31" s="18" t="s">
@@ -4344,10 +4348,10 @@
       <c r="H31" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="I31" s="97" t="s">
+      <c r="I31" s="141" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="97" t="s">
+      <c r="J31" s="141" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4376,8 +4380,8 @@
       <c r="H32" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="I32" s="98"/>
-      <c r="J32" s="98"/>
+      <c r="I32" s="146"/>
+      <c r="J32" s="146"/>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1">
       <c r="A33" s="18" t="s">
@@ -4386,10 +4390,10 @@
       <c r="B33" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="101" t="s">
+      <c r="C33" s="149" t="s">
         <v>248</v>
       </c>
-      <c r="D33" s="96"/>
+      <c r="D33" s="110"/>
       <c r="E33" s="36" t="s">
         <v>65</v>
       </c>
@@ -4402,28 +4406,28 @@
       <c r="H33" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="I33" s="99"/>
-      <c r="J33" s="99"/>
+      <c r="I33" s="144"/>
+      <c r="J33" s="144"/>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1">
       <c r="A34" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="101" t="s">
+      <c r="B34" s="149" t="s">
         <v>247</v>
       </c>
-      <c r="C34" s="95"/>
-      <c r="D34" s="95"/>
+      <c r="C34" s="109"/>
+      <c r="D34" s="109"/>
       <c r="E34" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="F34" s="126" t="s">
+      <c r="F34" s="147" t="s">
         <v>68</v>
       </c>
-      <c r="G34" s="95"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="95"/>
-      <c r="J34" s="96"/>
+      <c r="G34" s="109"/>
+      <c r="H34" s="109"/>
+      <c r="I34" s="109"/>
+      <c r="J34" s="110"/>
     </row>
     <row r="35" spans="1:10" ht="18" customHeight="1">
       <c r="A35" s="18" t="s">
@@ -4450,26 +4454,26 @@
       <c r="H35" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="I35" s="127" t="s">
+      <c r="I35" s="148" t="s">
         <v>309</v>
       </c>
-      <c r="J35" s="96"/>
+      <c r="J35" s="110"/>
     </row>
     <row r="36" spans="1:10" ht="18" customHeight="1">
       <c r="A36" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="101" t="s">
+      <c r="B36" s="149" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="124"/>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="124"/>
-      <c r="J36" s="125"/>
+      <c r="C36" s="150"/>
+      <c r="D36" s="150"/>
+      <c r="E36" s="150"/>
+      <c r="F36" s="150"/>
+      <c r="G36" s="150"/>
+      <c r="H36" s="150"/>
+      <c r="I36" s="150"/>
+      <c r="J36" s="151"/>
     </row>
     <row r="37" spans="1:10" ht="18" customHeight="1">
       <c r="A37" s="18" t="s">
@@ -4507,47 +4511,47 @@
       <c r="A38" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="104" t="s">
+      <c r="B38" s="162" t="s">
         <v>310</v>
       </c>
-      <c r="C38" s="124"/>
-      <c r="D38" s="124"/>
-      <c r="E38" s="124"/>
-      <c r="F38" s="124"/>
-      <c r="G38" s="124"/>
-      <c r="H38" s="124"/>
-      <c r="I38" s="124"/>
-      <c r="J38" s="125"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="150"/>
+      <c r="E38" s="150"/>
+      <c r="F38" s="150"/>
+      <c r="G38" s="150"/>
+      <c r="H38" s="150"/>
+      <c r="I38" s="150"/>
+      <c r="J38" s="151"/>
     </row>
     <row r="39" spans="1:10" ht="18" customHeight="1">
       <c r="A39" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="C39" s="95"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="95"/>
-      <c r="F39" s="95"/>
-      <c r="G39" s="95"/>
-      <c r="H39" s="95"/>
-      <c r="I39" s="95"/>
-      <c r="J39" s="96"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="109"/>
+      <c r="E39" s="109"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="109"/>
+      <c r="H39" s="109"/>
+      <c r="I39" s="109"/>
+      <c r="J39" s="110"/>
     </row>
     <row r="40" spans="1:10" ht="36" customHeight="1" thickBot="1">
-      <c r="A40" s="121" t="s">
+      <c r="A40" s="163" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="122"/>
-      <c r="C40" s="122"/>
-      <c r="D40" s="122"/>
-      <c r="E40" s="122"/>
-      <c r="F40" s="122"/>
-      <c r="G40" s="122"/>
-      <c r="H40" s="122"/>
-      <c r="I40" s="122"/>
-      <c r="J40" s="123"/>
+      <c r="B40" s="164"/>
+      <c r="C40" s="164"/>
+      <c r="D40" s="164"/>
+      <c r="E40" s="164"/>
+      <c r="F40" s="164"/>
+      <c r="G40" s="164"/>
+      <c r="H40" s="164"/>
+      <c r="I40" s="164"/>
+      <c r="J40" s="165"/>
     </row>
     <row r="41" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A41" s="5"/>
@@ -4601,17 +4605,17 @@
       <c r="A43" s="23">
         <v>0.25</v>
       </c>
-      <c r="B43" s="118" t="s">
+      <c r="B43" s="108" t="s">
         <v>251</v>
       </c>
-      <c r="C43" s="95"/>
-      <c r="D43" s="95"/>
-      <c r="E43" s="95"/>
-      <c r="F43" s="95"/>
-      <c r="G43" s="95"/>
-      <c r="H43" s="95"/>
-      <c r="I43" s="95"/>
-      <c r="J43" s="96"/>
+      <c r="C43" s="109"/>
+      <c r="D43" s="109"/>
+      <c r="E43" s="109"/>
+      <c r="F43" s="109"/>
+      <c r="G43" s="109"/>
+      <c r="H43" s="109"/>
+      <c r="I43" s="109"/>
+      <c r="J43" s="110"/>
     </row>
     <row r="44" spans="1:10" ht="16.5" customHeight="1">
       <c r="A44" s="23">
@@ -4681,21 +4685,21 @@
       <c r="A46" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="105" t="s">
+      <c r="B46" s="159" t="s">
         <v>254</v>
       </c>
-      <c r="C46" s="95"/>
-      <c r="D46" s="95"/>
-      <c r="E46" s="95"/>
-      <c r="F46" s="96"/>
-      <c r="G46" s="119" t="s">
+      <c r="C46" s="109"/>
+      <c r="D46" s="109"/>
+      <c r="E46" s="109"/>
+      <c r="F46" s="110"/>
+      <c r="G46" s="160" t="s">
         <v>93</v>
       </c>
-      <c r="H46" s="96"/>
-      <c r="I46" s="105" t="s">
+      <c r="H46" s="110"/>
+      <c r="I46" s="159" t="s">
         <v>92</v>
       </c>
-      <c r="J46" s="96"/>
+      <c r="J46" s="110"/>
     </row>
     <row r="47" spans="1:10" ht="16.5" customHeight="1">
       <c r="A47" s="18" t="s">
@@ -4707,21 +4711,21 @@
       <c r="C47" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="D47" s="120" t="s">
+      <c r="D47" s="161" t="s">
         <v>97</v>
       </c>
-      <c r="E47" s="95"/>
-      <c r="F47" s="96"/>
+      <c r="E47" s="109"/>
+      <c r="F47" s="110"/>
       <c r="G47" s="29" t="s">
         <v>98</v>
       </c>
       <c r="H47" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="I47" s="103" t="s">
+      <c r="I47" s="104" t="s">
         <v>257</v>
       </c>
-      <c r="J47" s="96"/>
+      <c r="J47" s="110"/>
     </row>
     <row r="48" spans="1:10" ht="16.5" customHeight="1">
       <c r="A48" s="18" t="s">
@@ -4730,11 +4734,11 @@
       <c r="B48" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="103" t="s">
+      <c r="C48" s="104" t="s">
         <v>260</v>
       </c>
-      <c r="D48" s="95"/>
-      <c r="E48" s="96"/>
+      <c r="D48" s="109"/>
+      <c r="E48" s="110"/>
       <c r="F48" s="29" t="s">
         <v>259</v>
       </c>
@@ -4790,22 +4794,22 @@
       <c r="B50" s="69" t="s">
         <v>265</v>
       </c>
-      <c r="C50" s="146" t="s">
+      <c r="C50" s="106" t="s">
         <v>103</v>
       </c>
-      <c r="D50" s="146" t="s">
+      <c r="D50" s="106" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="146" t="s">
+      <c r="E50" s="106" t="s">
         <v>103</v>
       </c>
-      <c r="F50" s="146" t="s">
+      <c r="F50" s="106" t="s">
         <v>103</v>
       </c>
-      <c r="G50" s="143" t="s">
+      <c r="G50" s="102" t="s">
         <v>280</v>
       </c>
-      <c r="H50" s="144"/>
+      <c r="H50" s="103"/>
       <c r="I50" s="65" t="s">
         <v>267</v>
       </c>
@@ -4820,10 +4824,10 @@
       <c r="B51" s="70" t="s">
         <v>258</v>
       </c>
-      <c r="C51" s="147"/>
-      <c r="D51" s="147"/>
-      <c r="E51" s="147"/>
-      <c r="F51" s="147"/>
+      <c r="C51" s="107"/>
+      <c r="D51" s="107"/>
+      <c r="E51" s="107"/>
+      <c r="F51" s="107"/>
       <c r="G51" s="66" t="s">
         <v>258</v>
       </c>
@@ -4841,17 +4845,17 @@
       <c r="A52" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="116" t="s">
+      <c r="B52" s="157" t="s">
         <v>185</v>
       </c>
-      <c r="C52" s="95"/>
-      <c r="D52" s="95"/>
-      <c r="E52" s="95"/>
-      <c r="F52" s="95"/>
-      <c r="G52" s="102"/>
-      <c r="H52" s="95"/>
-      <c r="I52" s="102"/>
-      <c r="J52" s="117"/>
+      <c r="C52" s="109"/>
+      <c r="D52" s="109"/>
+      <c r="E52" s="109"/>
+      <c r="F52" s="109"/>
+      <c r="G52" s="136"/>
+      <c r="H52" s="109"/>
+      <c r="I52" s="136"/>
+      <c r="J52" s="158"/>
     </row>
     <row r="53" spans="1:10" ht="16.5" customHeight="1">
       <c r="A53" s="18" t="s">
@@ -4863,19 +4867,19 @@
       <c r="C53" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D53" s="115" t="s">
+      <c r="D53" s="156" t="s">
         <v>108</v>
       </c>
-      <c r="E53" s="115" t="s">
+      <c r="E53" s="156" t="s">
         <v>108</v>
       </c>
-      <c r="F53" s="115" t="s">
+      <c r="F53" s="156" t="s">
         <v>108</v>
       </c>
       <c r="G53" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="H53" s="115" t="s">
+      <c r="H53" s="156" t="s">
         <v>108</v>
       </c>
       <c r="I53" s="36" t="s">
@@ -4893,13 +4897,13 @@
       <c r="C54" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="D54" s="99"/>
-      <c r="E54" s="99"/>
-      <c r="F54" s="99"/>
+      <c r="D54" s="144"/>
+      <c r="E54" s="144"/>
+      <c r="F54" s="144"/>
       <c r="G54" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="H54" s="99"/>
+      <c r="H54" s="144"/>
       <c r="I54" s="36" t="s">
         <v>112</v>
       </c>
@@ -4914,16 +4918,16 @@
       <c r="B55" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="C55" s="140" t="s">
+      <c r="C55" s="99" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="140"/>
-      <c r="E55" s="140"/>
-      <c r="F55" s="140"/>
-      <c r="G55" s="140"/>
-      <c r="H55" s="141"/>
-      <c r="I55" s="140"/>
-      <c r="J55" s="142"/>
+      <c r="D55" s="99"/>
+      <c r="E55" s="99"/>
+      <c r="F55" s="99"/>
+      <c r="G55" s="99"/>
+      <c r="H55" s="100"/>
+      <c r="I55" s="99"/>
+      <c r="J55" s="101"/>
     </row>
     <row r="56" spans="1:10" ht="16.5" customHeight="1">
       <c r="A56" s="23">
@@ -5034,10 +5038,10 @@
       <c r="F59" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="G59" s="103" t="s">
+      <c r="G59" s="104" t="s">
         <v>281</v>
       </c>
-      <c r="H59" s="145"/>
+      <c r="H59" s="105"/>
       <c r="I59" s="29" t="s">
         <v>126</v>
       </c>
@@ -5049,25 +5053,25 @@
       <c r="A60" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="B60" s="100" t="s">
+      <c r="B60" s="115" t="s">
         <v>129</v>
       </c>
-      <c r="C60" s="148"/>
+      <c r="C60" s="116"/>
       <c r="D60" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="E60" s="100" t="s">
+      <c r="E60" s="115" t="s">
         <v>129</v>
       </c>
-      <c r="F60" s="95"/>
-      <c r="G60" s="100" t="s">
+      <c r="F60" s="109"/>
+      <c r="G60" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="H60" s="95"/>
-      <c r="I60" s="100" t="s">
+      <c r="H60" s="109"/>
+      <c r="I60" s="115" t="s">
         <v>129</v>
       </c>
-      <c r="J60" s="95"/>
+      <c r="J60" s="109"/>
     </row>
     <row r="61" spans="1:10" ht="16.5">
       <c r="A61" s="18" t="s">
@@ -5169,47 +5173,47 @@
       <c r="A64" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B64" s="129" t="s">
+      <c r="B64" s="135" t="s">
         <v>311</v>
       </c>
-      <c r="C64" s="102"/>
-      <c r="D64" s="102"/>
-      <c r="E64" s="102"/>
-      <c r="F64" s="102"/>
-      <c r="G64" s="102"/>
-      <c r="H64" s="102"/>
-      <c r="I64" s="102"/>
-      <c r="J64" s="102"/>
+      <c r="C64" s="136"/>
+      <c r="D64" s="136"/>
+      <c r="E64" s="136"/>
+      <c r="F64" s="136"/>
+      <c r="G64" s="136"/>
+      <c r="H64" s="136"/>
+      <c r="I64" s="136"/>
+      <c r="J64" s="136"/>
     </row>
     <row r="65" spans="1:10" ht="18" customHeight="1">
       <c r="A65" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B65" s="94" t="s">
+      <c r="B65" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="C65" s="95"/>
-      <c r="D65" s="95"/>
-      <c r="E65" s="95"/>
-      <c r="F65" s="95"/>
-      <c r="G65" s="95"/>
-      <c r="H65" s="95"/>
-      <c r="I65" s="95"/>
-      <c r="J65" s="96"/>
+      <c r="C65" s="109"/>
+      <c r="D65" s="109"/>
+      <c r="E65" s="109"/>
+      <c r="F65" s="109"/>
+      <c r="G65" s="109"/>
+      <c r="H65" s="109"/>
+      <c r="I65" s="109"/>
+      <c r="J65" s="110"/>
     </row>
     <row r="66" spans="1:10" ht="36" customHeight="1" thickBot="1">
-      <c r="A66" s="149" t="s">
+      <c r="A66" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="B66" s="95"/>
-      <c r="C66" s="95"/>
-      <c r="D66" s="95"/>
-      <c r="E66" s="95"/>
-      <c r="F66" s="95"/>
-      <c r="G66" s="95"/>
-      <c r="H66" s="95"/>
-      <c r="I66" s="95"/>
-      <c r="J66" s="96"/>
+      <c r="B66" s="109"/>
+      <c r="C66" s="109"/>
+      <c r="D66" s="109"/>
+      <c r="E66" s="109"/>
+      <c r="F66" s="109"/>
+      <c r="G66" s="109"/>
+      <c r="H66" s="109"/>
+      <c r="I66" s="109"/>
+      <c r="J66" s="110"/>
     </row>
     <row r="67" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A67" s="5"/>
@@ -5263,15 +5267,15 @@
       <c r="A69" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B69" s="118" t="s">
+      <c r="B69" s="108" t="s">
         <v>184</v>
       </c>
-      <c r="C69" s="95"/>
-      <c r="D69" s="95"/>
-      <c r="E69" s="95"/>
-      <c r="F69" s="95"/>
-      <c r="G69" s="95"/>
-      <c r="H69" s="96"/>
+      <c r="C69" s="109"/>
+      <c r="D69" s="109"/>
+      <c r="E69" s="109"/>
+      <c r="F69" s="109"/>
+      <c r="G69" s="109"/>
+      <c r="H69" s="110"/>
       <c r="I69" s="49"/>
       <c r="J69" s="49"/>
     </row>
@@ -5300,10 +5304,10 @@
       <c r="H70" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="I70" s="103" t="s">
+      <c r="I70" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="J70" s="96"/>
+      <c r="J70" s="110"/>
     </row>
     <row r="71" spans="1:10" ht="16.5">
       <c r="A71" s="18" t="s">
@@ -5315,10 +5319,10 @@
       <c r="C71" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="D71" s="103" t="s">
+      <c r="D71" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="E71" s="106"/>
+      <c r="E71" s="132"/>
       <c r="F71" s="83" t="s">
         <v>315</v>
       </c>
@@ -5333,19 +5337,19 @@
       <c r="A72" s="68" t="s">
         <v>139</v>
       </c>
-      <c r="B72" s="85" t="s">
+      <c r="B72" s="166" t="s">
         <v>314</v>
       </c>
-      <c r="C72" s="87" t="s">
+      <c r="C72" s="168" t="s">
         <v>314</v>
       </c>
-      <c r="D72" s="90" t="s">
+      <c r="D72" s="171" t="s">
         <v>315</v>
       </c>
-      <c r="E72" s="88" t="s">
+      <c r="E72" s="169" t="s">
         <v>315</v>
       </c>
-      <c r="F72" s="92" t="s">
+      <c r="F72" s="173" t="s">
         <v>314</v>
       </c>
       <c r="G72" s="84" t="s">
@@ -5354,20 +5358,20 @@
       <c r="H72" s="76" t="s">
         <v>314</v>
       </c>
-      <c r="I72" s="103" t="s">
+      <c r="I72" s="104" t="s">
         <v>140</v>
       </c>
-      <c r="J72" s="96"/>
+      <c r="J72" s="110"/>
     </row>
     <row r="73" spans="1:10" ht="16.5" customHeight="1">
       <c r="A73" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="B73" s="86"/>
-      <c r="C73" s="86"/>
-      <c r="D73" s="91"/>
-      <c r="E73" s="89"/>
-      <c r="F73" s="93"/>
+      <c r="B73" s="167"/>
+      <c r="C73" s="167"/>
+      <c r="D73" s="172"/>
+      <c r="E73" s="170"/>
+      <c r="F73" s="174"/>
       <c r="G73" s="82" t="s">
         <v>316</v>
       </c>
@@ -5381,17 +5385,17 @@
       <c r="A74" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B74" s="100" t="s">
+      <c r="B74" s="115" t="s">
         <v>144</v>
       </c>
-      <c r="C74" s="95"/>
-      <c r="D74" s="95"/>
-      <c r="E74" s="102"/>
-      <c r="F74" s="102"/>
-      <c r="G74" s="95"/>
-      <c r="H74" s="95"/>
-      <c r="I74" s="95"/>
-      <c r="J74" s="96"/>
+      <c r="C74" s="109"/>
+      <c r="D74" s="109"/>
+      <c r="E74" s="136"/>
+      <c r="F74" s="136"/>
+      <c r="G74" s="109"/>
+      <c r="H74" s="109"/>
+      <c r="I74" s="109"/>
+      <c r="J74" s="110"/>
     </row>
     <row r="75" spans="1:10" ht="16.5" customHeight="1">
       <c r="A75" s="18" t="s">
@@ -5418,10 +5422,10 @@
       <c r="H75" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="I75" s="97" t="s">
+      <c r="I75" s="141" t="s">
         <v>90</v>
       </c>
-      <c r="J75" s="97" t="s">
+      <c r="J75" s="141" t="s">
         <v>90</v>
       </c>
     </row>
@@ -5435,47 +5439,47 @@
       <c r="C76" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="D76" s="101" t="s">
+      <c r="D76" s="149" t="s">
         <v>149</v>
       </c>
-      <c r="E76" s="95"/>
-      <c r="F76" s="95"/>
-      <c r="G76" s="95"/>
-      <c r="H76" s="96"/>
-      <c r="I76" s="99"/>
-      <c r="J76" s="99"/>
+      <c r="E76" s="109"/>
+      <c r="F76" s="109"/>
+      <c r="G76" s="109"/>
+      <c r="H76" s="110"/>
+      <c r="I76" s="144"/>
+      <c r="J76" s="144"/>
     </row>
     <row r="77" spans="1:10" ht="16.5" customHeight="1">
       <c r="A77" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="B77" s="100" t="s">
+      <c r="B77" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="C77" s="95"/>
-      <c r="D77" s="95"/>
-      <c r="E77" s="95"/>
-      <c r="F77" s="95"/>
-      <c r="G77" s="95"/>
-      <c r="H77" s="95"/>
-      <c r="I77" s="95"/>
-      <c r="J77" s="96"/>
+      <c r="C77" s="109"/>
+      <c r="D77" s="109"/>
+      <c r="E77" s="109"/>
+      <c r="F77" s="109"/>
+      <c r="G77" s="109"/>
+      <c r="H77" s="109"/>
+      <c r="I77" s="109"/>
+      <c r="J77" s="110"/>
     </row>
     <row r="78" spans="1:10" ht="16.5" customHeight="1">
       <c r="A78" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="B78" s="103" t="s">
+      <c r="B78" s="104" t="s">
         <v>152</v>
       </c>
-      <c r="C78" s="95"/>
-      <c r="D78" s="95"/>
-      <c r="E78" s="95"/>
-      <c r="F78" s="95"/>
-      <c r="G78" s="95"/>
-      <c r="H78" s="95"/>
-      <c r="I78" s="95"/>
-      <c r="J78" s="96"/>
+      <c r="C78" s="109"/>
+      <c r="D78" s="109"/>
+      <c r="E78" s="109"/>
+      <c r="F78" s="109"/>
+      <c r="G78" s="109"/>
+      <c r="H78" s="109"/>
+      <c r="I78" s="109"/>
+      <c r="J78" s="110"/>
     </row>
     <row r="79" spans="1:10" ht="16.5" customHeight="1">
       <c r="A79" s="18" t="s">
@@ -5517,21 +5521,21 @@
       <c r="H80" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="I80" s="104" t="s">
+      <c r="I80" s="162" t="s">
         <v>153</v>
       </c>
-      <c r="J80" s="96"/>
+      <c r="J80" s="110"/>
     </row>
     <row r="81" spans="1:10" ht="16.5" customHeight="1">
       <c r="A81" s="68" t="s">
         <v>312</v>
       </c>
-      <c r="B81" s="139" t="s">
+      <c r="B81" s="98" t="s">
         <v>297</v>
       </c>
-      <c r="C81" s="139"/>
-      <c r="D81" s="139"/>
-      <c r="E81" s="139"/>
+      <c r="C81" s="98"/>
+      <c r="D81" s="98"/>
+      <c r="E81" s="98"/>
       <c r="F81" s="51" t="s">
         <v>296</v>
       </c>
@@ -5646,17 +5650,17 @@
       <c r="A86" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B86" s="94" t="s">
+      <c r="B86" s="118" t="s">
         <v>162</v>
       </c>
-      <c r="C86" s="95"/>
-      <c r="D86" s="95"/>
-      <c r="E86" s="95"/>
-      <c r="F86" s="95"/>
-      <c r="G86" s="95"/>
-      <c r="H86" s="95"/>
-      <c r="I86" s="95"/>
-      <c r="J86" s="96"/>
+      <c r="C86" s="109"/>
+      <c r="D86" s="109"/>
+      <c r="E86" s="109"/>
+      <c r="F86" s="109"/>
+      <c r="G86" s="109"/>
+      <c r="H86" s="109"/>
+      <c r="I86" s="109"/>
+      <c r="J86" s="110"/>
     </row>
     <row r="87" spans="1:10" ht="16.5" customHeight="1">
       <c r="A87" s="1"/>
@@ -8790,6 +8794,71 @@
     <row r="1016" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="81">
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="B86:J86"/>
+    <mergeCell ref="I27:I29"/>
+    <mergeCell ref="B77:J77"/>
+    <mergeCell ref="D76:H76"/>
+    <mergeCell ref="B74:J74"/>
+    <mergeCell ref="J75:J76"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="B78:J78"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B38:J38"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="B52:J52"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="B43:J43"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B64:J64"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="J27:J29"/>
+    <mergeCell ref="I31:I33"/>
+    <mergeCell ref="J31:J33"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="H22:H24"/>
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="C55:J55"/>
     <mergeCell ref="G50:H50"/>
@@ -8806,71 +8875,6 @@
     <mergeCell ref="I60:J60"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="B65:J65"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="B64:J64"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="B39:J39"/>
-    <mergeCell ref="J27:J29"/>
-    <mergeCell ref="I31:I33"/>
-    <mergeCell ref="J31:J33"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="F53:F54"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="B52:J52"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="B43:J43"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="B86:J86"/>
-    <mergeCell ref="I27:I29"/>
-    <mergeCell ref="B77:J77"/>
-    <mergeCell ref="D76:H76"/>
-    <mergeCell ref="B74:J74"/>
-    <mergeCell ref="J75:J76"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="B78:J78"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B38:J38"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="F72:F73"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -8903,126 +8907,128 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="86" t="s">
         <v>323</v>
       </c>
-      <c r="C2" s="151" t="s">
+      <c r="C2" s="86" t="s">
         <v>324</v>
       </c>
-      <c r="D2" s="151" t="s">
+      <c r="D2" s="86" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A3" s="152" t="s">
+      <c r="A3" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="153" t="s">
+      <c r="B3" s="88" t="s">
         <v>325</v>
       </c>
-      <c r="C3" s="153" t="s">
+      <c r="C3" s="88" t="s">
         <v>326</v>
       </c>
-      <c r="D3" s="154"/>
+      <c r="D3" s="89" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A4" s="152" t="s">
+      <c r="A4" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="153" t="s">
+      <c r="B4" s="88" t="s">
         <v>327</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="88" t="s">
         <v>328</v>
       </c>
-      <c r="D4" s="153" t="s">
+      <c r="D4" s="88" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="153" t="s">
+      <c r="B5" s="88" t="s">
         <v>330</v>
       </c>
-      <c r="C5" s="153" t="s">
+      <c r="C5" s="88" t="s">
         <v>331</v>
       </c>
-      <c r="D5" s="153" t="s">
+      <c r="D5" s="88" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A6" s="152" t="s">
+      <c r="A6" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="153" t="s">
+      <c r="B6" s="88" t="s">
         <v>333</v>
       </c>
-      <c r="C6" s="153" t="s">
+      <c r="C6" s="88" t="s">
         <v>334</v>
       </c>
-      <c r="D6" s="153" t="s">
+      <c r="D6" s="88" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A7" s="152" t="s">
+      <c r="A7" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="153" t="s">
+      <c r="B7" s="88" t="s">
         <v>336</v>
       </c>
-      <c r="C7" s="153" t="s">
+      <c r="C7" s="88" t="s">
         <v>337</v>
       </c>
-      <c r="D7" s="153" t="s">
+      <c r="D7" s="88" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A8" s="152" t="s">
+      <c r="A8" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="153" t="s">
+      <c r="B8" s="88" t="s">
         <v>339</v>
       </c>
-      <c r="C8" s="153" t="s">
+      <c r="C8" s="88" t="s">
         <v>340</v>
       </c>
-      <c r="D8" s="153" t="s">
+      <c r="D8" s="88" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A9" s="152" t="s">
+      <c r="A9" s="87" t="s">
         <v>342</v>
       </c>
-      <c r="B9" s="153" t="s">
+      <c r="B9" s="88" t="s">
         <v>343</v>
       </c>
-      <c r="C9" s="153" t="s">
+      <c r="C9" s="88" t="s">
         <v>344</v>
       </c>
-      <c r="D9" s="153" t="s">
+      <c r="D9" s="88" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A10" s="152" t="s">
+      <c r="A10" s="87" t="s">
         <v>342</v>
       </c>
-      <c r="B10" s="153" t="s">
+      <c r="B10" s="88" t="s">
         <v>346</v>
       </c>
-      <c r="C10" s="153" t="s">
+      <c r="C10" s="88" t="s">
         <v>347</v>
       </c>
-      <c r="D10" s="153" t="s">
+      <c r="D10" s="88" t="s">
         <v>348</v>
       </c>
     </row>
@@ -9045,422 +9051,422 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="96" t="s">
         <v>350</v>
       </c>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="96" t="s">
         <v>317</v>
       </c>
-      <c r="C1" s="161" t="s">
+      <c r="C1" s="96" t="s">
         <v>320</v>
       </c>
-      <c r="D1" s="161" t="s">
+      <c r="D1" s="96" t="s">
         <v>351</v>
       </c>
-      <c r="E1" s="161" t="s">
+      <c r="E1" s="96" t="s">
         <v>394</v>
       </c>
-      <c r="F1" s="161" t="s">
+      <c r="F1" s="96" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="90" t="s">
         <v>352</v>
       </c>
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="90" t="s">
         <v>353</v>
       </c>
-      <c r="C2" s="155" t="s">
+      <c r="C2" s="90" t="s">
         <v>354</v>
       </c>
-      <c r="D2" s="155" t="s">
+      <c r="D2" s="90" t="s">
         <v>355</v>
       </c>
-      <c r="E2" s="155" t="s">
+      <c r="E2" s="90" t="s">
         <v>396</v>
       </c>
-      <c r="F2" s="155" t="s">
+      <c r="F2" s="90" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="90" t="s">
         <v>352</v>
       </c>
-      <c r="B3" s="156" t="s">
+      <c r="B3" s="91" t="s">
         <v>356</v>
       </c>
-      <c r="C3" s="155" t="s">
+      <c r="C3" s="90" t="s">
         <v>357</v>
       </c>
-      <c r="D3" s="155" t="s">
+      <c r="D3" s="90" t="s">
         <v>355</v>
       </c>
-      <c r="E3" s="155" t="s">
+      <c r="E3" s="90" t="s">
         <v>398</v>
       </c>
-      <c r="F3" s="155" t="s">
+      <c r="F3" s="90" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="155" t="s">
+      <c r="A4" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B4" s="157" t="s">
+      <c r="B4" s="92" t="s">
         <v>359</v>
       </c>
-      <c r="C4" s="155" t="s">
+      <c r="C4" s="90" t="s">
         <v>360</v>
       </c>
-      <c r="D4" s="155" t="s">
+      <c r="D4" s="90" t="s">
         <v>361</v>
       </c>
-      <c r="E4" s="155" t="s">
+      <c r="E4" s="90" t="s">
         <v>400</v>
       </c>
-      <c r="F4" s="155" t="s">
+      <c r="F4" s="90" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="155" t="s">
+      <c r="A5" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B5" s="155" t="s">
+      <c r="B5" s="90" t="s">
         <v>362</v>
       </c>
-      <c r="C5" s="155" t="s">
+      <c r="C5" s="90" t="s">
         <v>363</v>
       </c>
-      <c r="D5" s="155" t="s">
+      <c r="D5" s="90" t="s">
         <v>355</v>
       </c>
-      <c r="E5" s="155" t="s">
+      <c r="E5" s="90" t="s">
         <v>402</v>
       </c>
-      <c r="F5" s="155" t="s">
+      <c r="F5" s="90" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="155" t="s">
+      <c r="A6" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B6" s="158" t="s">
+      <c r="B6" s="93" t="s">
         <v>364</v>
       </c>
-      <c r="C6" s="158" t="s">
+      <c r="C6" s="93" t="s">
         <v>365</v>
       </c>
-      <c r="D6" s="155" t="s">
+      <c r="D6" s="90" t="s">
         <v>355</v>
       </c>
-      <c r="E6" s="155" t="s">
+      <c r="E6" s="90" t="s">
         <v>404</v>
       </c>
-      <c r="F6" s="155" t="s">
+      <c r="F6" s="90" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="155" t="s">
+      <c r="A7" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B7" s="159" t="s">
+      <c r="B7" s="94" t="s">
         <v>366</v>
       </c>
-      <c r="C7" s="155" t="s">
+      <c r="C7" s="90" t="s">
         <v>367</v>
       </c>
-      <c r="D7" s="155" t="s">
+      <c r="D7" s="90" t="s">
         <v>355</v>
       </c>
-      <c r="E7" s="155" t="s">
+      <c r="E7" s="90" t="s">
         <v>406</v>
       </c>
-      <c r="F7" s="155" t="s">
+      <c r="F7" s="90" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="155" t="s">
+      <c r="A8" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B8" s="159" t="s">
+      <c r="B8" s="94" t="s">
         <v>368</v>
       </c>
-      <c r="C8" s="155" t="s">
+      <c r="C8" s="90" t="s">
         <v>367</v>
       </c>
-      <c r="D8" s="155" t="s">
+      <c r="D8" s="90" t="s">
         <v>355</v>
       </c>
-      <c r="E8" s="155" t="s">
+      <c r="E8" s="90" t="s">
         <v>408</v>
       </c>
-      <c r="F8" s="155" t="s">
+      <c r="F8" s="90" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B9" s="158" t="s">
+      <c r="B9" s="93" t="s">
         <v>369</v>
       </c>
-      <c r="C9" s="158" t="s">
+      <c r="C9" s="93" t="s">
         <v>370</v>
       </c>
-      <c r="D9" s="155" t="s">
+      <c r="D9" s="90" t="s">
         <v>361</v>
       </c>
-      <c r="E9" s="155" t="s">
+      <c r="E9" s="90" t="s">
         <v>409</v>
       </c>
-      <c r="F9" s="155" t="s">
+      <c r="F9" s="90" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="155" t="s">
+      <c r="A10" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B10" s="155" t="s">
+      <c r="B10" s="90" t="s">
         <v>371</v>
       </c>
-      <c r="C10" s="155" t="s">
+      <c r="C10" s="90" t="s">
         <v>372</v>
       </c>
-      <c r="D10" s="155" t="s">
+      <c r="D10" s="90" t="s">
         <v>361</v>
       </c>
-      <c r="E10" s="155" t="s">
+      <c r="E10" s="90" t="s">
         <v>410</v>
       </c>
-      <c r="F10" s="155" t="s">
+      <c r="F10" s="90" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="155" t="s">
+      <c r="A11" s="90" t="s">
         <v>374</v>
       </c>
-      <c r="B11" s="157" t="s">
+      <c r="B11" s="92" t="s">
         <v>375</v>
       </c>
-      <c r="C11" s="155" t="s">
+      <c r="C11" s="90" t="s">
         <v>376</v>
       </c>
-      <c r="D11" s="155" t="s">
+      <c r="D11" s="90" t="s">
         <v>355</v>
       </c>
-      <c r="E11" s="155" t="s">
+      <c r="E11" s="90" t="s">
         <v>412</v>
       </c>
-      <c r="F11" s="155" t="s">
+      <c r="F11" s="90" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="155" t="s">
+      <c r="A12" s="90" t="s">
         <v>374</v>
       </c>
-      <c r="B12" s="155" t="s">
+      <c r="B12" s="90" t="s">
         <v>377</v>
       </c>
-      <c r="C12" s="155" t="s">
+      <c r="C12" s="90" t="s">
         <v>378</v>
       </c>
-      <c r="D12" s="155" t="s">
+      <c r="D12" s="90" t="s">
         <v>355</v>
       </c>
-      <c r="E12" s="155" t="s">
+      <c r="E12" s="90" t="s">
         <v>413</v>
       </c>
-      <c r="F12" s="155" t="s">
+      <c r="F12" s="90" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="155" t="s">
+      <c r="A13" s="90" t="s">
         <v>374</v>
       </c>
-      <c r="B13" s="155" t="s">
+      <c r="B13" s="90" t="s">
         <v>379</v>
       </c>
-      <c r="C13" s="155" t="s">
+      <c r="C13" s="90" t="s">
         <v>380</v>
       </c>
-      <c r="D13" s="155" t="s">
+      <c r="D13" s="90" t="s">
         <v>361</v>
       </c>
-      <c r="E13" s="155" t="s">
+      <c r="E13" s="90" t="s">
         <v>415</v>
       </c>
-      <c r="F13" s="155" t="s">
+      <c r="F13" s="90" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="155" t="s">
+      <c r="A14" s="90" t="s">
         <v>374</v>
       </c>
-      <c r="B14" s="155" t="s">
+      <c r="B14" s="90" t="s">
         <v>381</v>
       </c>
-      <c r="C14" s="155" t="s">
+      <c r="C14" s="90" t="s">
         <v>382</v>
       </c>
-      <c r="D14" s="155" t="s">
+      <c r="D14" s="90" t="s">
         <v>355</v>
       </c>
-      <c r="E14" s="155" t="s">
+      <c r="E14" s="90" t="s">
         <v>417</v>
       </c>
-      <c r="F14" s="155" t="s">
+      <c r="F14" s="90" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="155" t="s">
+      <c r="A15" s="90" t="s">
         <v>383</v>
       </c>
-      <c r="B15" s="155" t="s">
+      <c r="B15" s="90" t="s">
         <v>384</v>
       </c>
-      <c r="C15" s="155" t="s">
+      <c r="C15" s="90" t="s">
         <v>385</v>
       </c>
-      <c r="D15" s="155" t="s">
+      <c r="D15" s="90" t="s">
         <v>361</v>
       </c>
-      <c r="E15" s="155" t="s">
+      <c r="E15" s="90" t="s">
         <v>419</v>
       </c>
-      <c r="F15" s="155" t="s">
+      <c r="F15" s="90" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="155" t="s">
+      <c r="A16" s="90" t="s">
         <v>383</v>
       </c>
-      <c r="B16" s="155" t="s">
+      <c r="B16" s="90" t="s">
         <v>386</v>
       </c>
-      <c r="C16" s="155" t="s">
+      <c r="C16" s="90" t="s">
         <v>387</v>
       </c>
-      <c r="D16" s="155" t="s">
+      <c r="D16" s="90" t="s">
         <v>361</v>
       </c>
-      <c r="E16" s="155" t="s">
+      <c r="E16" s="90" t="s">
         <v>421</v>
       </c>
-      <c r="F16" s="155" t="s">
+      <c r="F16" s="90" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="155" t="s">
+      <c r="A17" s="90" t="s">
         <v>383</v>
       </c>
-      <c r="B17" s="155" t="s">
+      <c r="B17" s="90" t="s">
         <v>388</v>
       </c>
-      <c r="C17" s="155" t="s">
+      <c r="C17" s="90" t="s">
         <v>367</v>
       </c>
-      <c r="D17" s="155" t="s">
+      <c r="D17" s="90" t="s">
         <v>361</v>
       </c>
-      <c r="E17" s="155" t="s">
+      <c r="E17" s="90" t="s">
         <v>423</v>
       </c>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="90" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="155" t="s">
+      <c r="A18" s="90" t="s">
         <v>383</v>
       </c>
-      <c r="B18" s="155" t="s">
+      <c r="B18" s="90" t="s">
         <v>389</v>
       </c>
-      <c r="C18" s="155" t="s">
+      <c r="C18" s="90" t="s">
         <v>373</v>
       </c>
-      <c r="D18" s="155" t="s">
+      <c r="D18" s="90" t="s">
         <v>361</v>
       </c>
-      <c r="E18" s="155" t="s">
+      <c r="E18" s="90" t="s">
         <v>425</v>
       </c>
-      <c r="F18" s="155" t="s">
+      <c r="F18" s="90" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="155" t="s">
+      <c r="A19" s="90" t="s">
         <v>383</v>
       </c>
-      <c r="B19" s="155" t="s">
+      <c r="B19" s="90" t="s">
         <v>390</v>
       </c>
-      <c r="C19" s="155" t="s">
+      <c r="C19" s="90" t="s">
         <v>391</v>
       </c>
-      <c r="D19" s="155" t="s">
+      <c r="D19" s="90" t="s">
         <v>361</v>
       </c>
-      <c r="E19" s="155" t="s">
+      <c r="E19" s="90" t="s">
         <v>427</v>
       </c>
-      <c r="F19" s="155" t="s">
+      <c r="F19" s="90" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="155" t="s">
+      <c r="A20" s="90" t="s">
         <v>383</v>
       </c>
-      <c r="B20" s="156" t="s">
+      <c r="B20" s="91" t="s">
         <v>392</v>
       </c>
-      <c r="C20" s="155" t="s">
+      <c r="C20" s="90" t="s">
         <v>373</v>
       </c>
-      <c r="D20" s="155" t="s">
+      <c r="D20" s="90" t="s">
         <v>361</v>
       </c>
-      <c r="E20" s="155" t="s">
+      <c r="E20" s="90" t="s">
         <v>429</v>
       </c>
-      <c r="F20" s="155" t="s">
+      <c r="F20" s="90" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="155" t="s">
+      <c r="A21" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B21" s="155" t="s">
+      <c r="B21" s="90" t="s">
         <v>393</v>
       </c>
-      <c r="C21" s="155" t="s">
+      <c r="C21" s="90" t="s">
         <v>367</v>
       </c>
-      <c r="D21" s="155" t="s">
+      <c r="D21" s="90" t="s">
         <v>355</v>
       </c>
-      <c r="E21" s="160" t="s">
+      <c r="E21" s="95" t="s">
         <v>430</v>
       </c>
-      <c r="F21" s="160" t="s">
+      <c r="F21" s="95" t="s">
         <v>431</v>
       </c>
     </row>

--- a/2026 여름신앙학교 데일리 스케줄(최종).xlsx
+++ b/2026 여름신앙학교 데일리 스케줄(최종).xlsx
@@ -3025,122 +3025,134 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3154,106 +3166,94 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3490,48 +3490,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="153"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="127" t="s">
         <v>178</v>
       </c>
-      <c r="B2" s="155"/>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A3" s="5"/>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="111" t="s">
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="112"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="114"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="132"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="6" t="s">
@@ -4105,25 +4105,25 @@
       <c r="A22" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="B22" s="141" t="s">
+      <c r="B22" s="110" t="s">
         <v>164</v>
       </c>
-      <c r="C22" s="139" t="s">
+      <c r="C22" s="143" t="s">
         <v>232</v>
       </c>
-      <c r="D22" s="123" t="s">
+      <c r="D22" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="126" t="s">
+      <c r="E22" s="156" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="129" t="s">
+      <c r="F22" s="159" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="137" t="s">
+      <c r="G22" s="141" t="s">
         <v>233</v>
       </c>
-      <c r="H22" s="132" t="s">
+      <c r="H22" s="119" t="s">
         <v>46</v>
       </c>
       <c r="I22" s="57" t="s">
@@ -4137,17 +4137,17 @@
       <c r="A23" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="B23" s="142"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="127"/>
-      <c r="F23" s="130"/>
-      <c r="G23" s="138"/>
-      <c r="H23" s="133"/>
-      <c r="I23" s="121" t="s">
+      <c r="B23" s="145"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="154"/>
+      <c r="E23" s="157"/>
+      <c r="F23" s="160"/>
+      <c r="G23" s="142"/>
+      <c r="H23" s="162"/>
+      <c r="I23" s="151" t="s">
         <v>234</v>
       </c>
-      <c r="J23" s="119" t="s">
+      <c r="J23" s="149" t="s">
         <v>234</v>
       </c>
     </row>
@@ -4155,19 +4155,19 @@
       <c r="A24" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="B24" s="143"/>
+      <c r="B24" s="146"/>
       <c r="C24" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="125"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="131"/>
+      <c r="D24" s="155"/>
+      <c r="E24" s="158"/>
+      <c r="F24" s="161"/>
       <c r="G24" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="H24" s="134"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="120"/>
+      <c r="H24" s="163"/>
+      <c r="I24" s="152"/>
+      <c r="J24" s="150"/>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1">
       <c r="A25" s="39" t="s">
@@ -4237,7 +4237,7 @@
       <c r="A27" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="141" t="s">
+      <c r="B27" s="110" t="s">
         <v>50</v>
       </c>
       <c r="C27" s="60" t="s">
@@ -4258,10 +4258,10 @@
       <c r="H27" s="62" t="s">
         <v>200</v>
       </c>
-      <c r="I27" s="141" t="s">
+      <c r="I27" s="110" t="s">
         <v>245</v>
       </c>
-      <c r="J27" s="141" t="s">
+      <c r="J27" s="110" t="s">
         <v>246</v>
       </c>
     </row>
@@ -4269,27 +4269,27 @@
       <c r="A28" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="144"/>
-      <c r="C28" s="145" t="s">
+      <c r="B28" s="112"/>
+      <c r="C28" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="145" t="s">
+      <c r="D28" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="E28" s="145" t="s">
+      <c r="E28" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="145" t="s">
+      <c r="F28" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="145" t="s">
+      <c r="G28" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="H28" s="145" t="s">
+      <c r="H28" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="I28" s="146"/>
-      <c r="J28" s="146"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="111"/>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1">
       <c r="A29" s="18" t="s">
@@ -4298,30 +4298,30 @@
       <c r="B29" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="144"/>
-      <c r="D29" s="144"/>
-      <c r="E29" s="144"/>
-      <c r="F29" s="144"/>
-      <c r="G29" s="144"/>
-      <c r="H29" s="144"/>
-      <c r="I29" s="144"/>
-      <c r="J29" s="144"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="112"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="112"/>
+      <c r="H29" s="112"/>
+      <c r="I29" s="112"/>
+      <c r="J29" s="112"/>
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1">
       <c r="A30" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="118" t="s">
+      <c r="B30" s="107" t="s">
         <v>182</v>
       </c>
-      <c r="C30" s="109"/>
-      <c r="D30" s="109"/>
-      <c r="E30" s="109"/>
-      <c r="F30" s="109"/>
-      <c r="G30" s="109"/>
-      <c r="H30" s="109"/>
-      <c r="I30" s="109"/>
-      <c r="J30" s="110"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="108"/>
+      <c r="I30" s="108"/>
+      <c r="J30" s="109"/>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1">
       <c r="A31" s="18" t="s">
@@ -4348,10 +4348,10 @@
       <c r="H31" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="I31" s="141" t="s">
+      <c r="I31" s="110" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="141" t="s">
+      <c r="J31" s="110" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4380,8 +4380,8 @@
       <c r="H32" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="I32" s="146"/>
-      <c r="J32" s="146"/>
+      <c r="I32" s="111"/>
+      <c r="J32" s="111"/>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1">
       <c r="A33" s="18" t="s">
@@ -4390,10 +4390,10 @@
       <c r="B33" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="149" t="s">
+      <c r="C33" s="114" t="s">
         <v>248</v>
       </c>
-      <c r="D33" s="110"/>
+      <c r="D33" s="109"/>
       <c r="E33" s="36" t="s">
         <v>65</v>
       </c>
@@ -4406,28 +4406,28 @@
       <c r="H33" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="I33" s="144"/>
-      <c r="J33" s="144"/>
+      <c r="I33" s="112"/>
+      <c r="J33" s="112"/>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1">
       <c r="A34" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="149" t="s">
+      <c r="B34" s="114" t="s">
         <v>247</v>
       </c>
-      <c r="C34" s="109"/>
-      <c r="D34" s="109"/>
+      <c r="C34" s="108"/>
+      <c r="D34" s="108"/>
       <c r="E34" s="36" t="s">
         <v>69</v>
       </c>
       <c r="F34" s="147" t="s">
         <v>68</v>
       </c>
-      <c r="G34" s="109"/>
-      <c r="H34" s="109"/>
-      <c r="I34" s="109"/>
-      <c r="J34" s="110"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="108"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="109"/>
     </row>
     <row r="35" spans="1:10" ht="18" customHeight="1">
       <c r="A35" s="18" t="s">
@@ -4457,23 +4457,23 @@
       <c r="I35" s="148" t="s">
         <v>309</v>
       </c>
-      <c r="J35" s="110"/>
+      <c r="J35" s="109"/>
     </row>
     <row r="36" spans="1:10" ht="18" customHeight="1">
       <c r="A36" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="149" t="s">
+      <c r="B36" s="114" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="150"/>
-      <c r="D36" s="150"/>
-      <c r="E36" s="150"/>
-      <c r="F36" s="150"/>
-      <c r="G36" s="150"/>
-      <c r="H36" s="150"/>
-      <c r="I36" s="150"/>
-      <c r="J36" s="151"/>
+      <c r="C36" s="123"/>
+      <c r="D36" s="123"/>
+      <c r="E36" s="123"/>
+      <c r="F36" s="123"/>
+      <c r="G36" s="123"/>
+      <c r="H36" s="123"/>
+      <c r="I36" s="123"/>
+      <c r="J36" s="124"/>
     </row>
     <row r="37" spans="1:10" ht="18" customHeight="1">
       <c r="A37" s="18" t="s">
@@ -4511,63 +4511,63 @@
       <c r="A38" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="162" t="s">
+      <c r="B38" s="117" t="s">
         <v>310</v>
       </c>
-      <c r="C38" s="150"/>
-      <c r="D38" s="150"/>
-      <c r="E38" s="150"/>
-      <c r="F38" s="150"/>
-      <c r="G38" s="150"/>
-      <c r="H38" s="150"/>
-      <c r="I38" s="150"/>
-      <c r="J38" s="151"/>
+      <c r="C38" s="123"/>
+      <c r="D38" s="123"/>
+      <c r="E38" s="123"/>
+      <c r="F38" s="123"/>
+      <c r="G38" s="123"/>
+      <c r="H38" s="123"/>
+      <c r="I38" s="123"/>
+      <c r="J38" s="124"/>
     </row>
     <row r="39" spans="1:10" ht="18" customHeight="1">
       <c r="A39" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B39" s="118" t="s">
+      <c r="B39" s="107" t="s">
         <v>183</v>
       </c>
-      <c r="C39" s="109"/>
-      <c r="D39" s="109"/>
-      <c r="E39" s="109"/>
-      <c r="F39" s="109"/>
-      <c r="G39" s="109"/>
-      <c r="H39" s="109"/>
-      <c r="I39" s="109"/>
-      <c r="J39" s="110"/>
+      <c r="C39" s="108"/>
+      <c r="D39" s="108"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="108"/>
+      <c r="G39" s="108"/>
+      <c r="H39" s="108"/>
+      <c r="I39" s="108"/>
+      <c r="J39" s="109"/>
     </row>
     <row r="40" spans="1:10" ht="36" customHeight="1" thickBot="1">
-      <c r="A40" s="163" t="s">
+      <c r="A40" s="120" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="164"/>
-      <c r="C40" s="164"/>
-      <c r="D40" s="164"/>
-      <c r="E40" s="164"/>
-      <c r="F40" s="164"/>
-      <c r="G40" s="164"/>
-      <c r="H40" s="164"/>
-      <c r="I40" s="164"/>
-      <c r="J40" s="165"/>
+      <c r="B40" s="121"/>
+      <c r="C40" s="121"/>
+      <c r="D40" s="121"/>
+      <c r="E40" s="121"/>
+      <c r="F40" s="121"/>
+      <c r="G40" s="121"/>
+      <c r="H40" s="121"/>
+      <c r="I40" s="121"/>
+      <c r="J40" s="122"/>
     </row>
     <row r="41" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A41" s="5"/>
-      <c r="B41" s="111" t="s">
+      <c r="B41" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="C41" s="112"/>
-      <c r="D41" s="112"/>
-      <c r="E41" s="112"/>
-      <c r="F41" s="113"/>
-      <c r="G41" s="111" t="s">
+      <c r="C41" s="130"/>
+      <c r="D41" s="130"/>
+      <c r="E41" s="130"/>
+      <c r="F41" s="131"/>
+      <c r="G41" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="H41" s="112"/>
-      <c r="I41" s="112"/>
-      <c r="J41" s="114"/>
+      <c r="H41" s="130"/>
+      <c r="I41" s="130"/>
+      <c r="J41" s="132"/>
     </row>
     <row r="42" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A42" s="6" t="s">
@@ -4605,17 +4605,17 @@
       <c r="A43" s="23">
         <v>0.25</v>
       </c>
-      <c r="B43" s="108" t="s">
+      <c r="B43" s="136" t="s">
         <v>251</v>
       </c>
-      <c r="C43" s="109"/>
-      <c r="D43" s="109"/>
-      <c r="E43" s="109"/>
-      <c r="F43" s="109"/>
-      <c r="G43" s="109"/>
-      <c r="H43" s="109"/>
-      <c r="I43" s="109"/>
-      <c r="J43" s="110"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="108"/>
+      <c r="E43" s="108"/>
+      <c r="F43" s="108"/>
+      <c r="G43" s="108"/>
+      <c r="H43" s="108"/>
+      <c r="I43" s="108"/>
+      <c r="J43" s="109"/>
     </row>
     <row r="44" spans="1:10" ht="16.5" customHeight="1">
       <c r="A44" s="23">
@@ -4685,21 +4685,21 @@
       <c r="A46" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="159" t="s">
+      <c r="B46" s="118" t="s">
         <v>254</v>
       </c>
-      <c r="C46" s="109"/>
-      <c r="D46" s="109"/>
-      <c r="E46" s="109"/>
-      <c r="F46" s="110"/>
-      <c r="G46" s="160" t="s">
+      <c r="C46" s="108"/>
+      <c r="D46" s="108"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="109"/>
+      <c r="G46" s="137" t="s">
         <v>93</v>
       </c>
-      <c r="H46" s="110"/>
-      <c r="I46" s="159" t="s">
+      <c r="H46" s="109"/>
+      <c r="I46" s="118" t="s">
         <v>92</v>
       </c>
-      <c r="J46" s="110"/>
+      <c r="J46" s="109"/>
     </row>
     <row r="47" spans="1:10" ht="16.5" customHeight="1">
       <c r="A47" s="18" t="s">
@@ -4711,21 +4711,21 @@
       <c r="C47" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="D47" s="161" t="s">
+      <c r="D47" s="138" t="s">
         <v>97</v>
       </c>
-      <c r="E47" s="109"/>
-      <c r="F47" s="110"/>
+      <c r="E47" s="108"/>
+      <c r="F47" s="109"/>
       <c r="G47" s="29" t="s">
         <v>98</v>
       </c>
       <c r="H47" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="I47" s="104" t="s">
+      <c r="I47" s="116" t="s">
         <v>257</v>
       </c>
-      <c r="J47" s="110"/>
+      <c r="J47" s="109"/>
     </row>
     <row r="48" spans="1:10" ht="16.5" customHeight="1">
       <c r="A48" s="18" t="s">
@@ -4734,11 +4734,11 @@
       <c r="B48" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="104" t="s">
+      <c r="C48" s="116" t="s">
         <v>260</v>
       </c>
-      <c r="D48" s="109"/>
-      <c r="E48" s="110"/>
+      <c r="D48" s="108"/>
+      <c r="E48" s="109"/>
       <c r="F48" s="29" t="s">
         <v>259</v>
       </c>
@@ -4794,22 +4794,22 @@
       <c r="B50" s="69" t="s">
         <v>265</v>
       </c>
-      <c r="C50" s="106" t="s">
+      <c r="C50" s="171" t="s">
         <v>103</v>
       </c>
-      <c r="D50" s="106" t="s">
+      <c r="D50" s="171" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="106" t="s">
+      <c r="E50" s="171" t="s">
         <v>103</v>
       </c>
-      <c r="F50" s="106" t="s">
+      <c r="F50" s="171" t="s">
         <v>103</v>
       </c>
-      <c r="G50" s="102" t="s">
+      <c r="G50" s="168" t="s">
         <v>280</v>
       </c>
-      <c r="H50" s="103"/>
+      <c r="H50" s="169"/>
       <c r="I50" s="65" t="s">
         <v>267</v>
       </c>
@@ -4824,10 +4824,10 @@
       <c r="B51" s="70" t="s">
         <v>258</v>
       </c>
-      <c r="C51" s="107"/>
-      <c r="D51" s="107"/>
-      <c r="E51" s="107"/>
-      <c r="F51" s="107"/>
+      <c r="C51" s="172"/>
+      <c r="D51" s="172"/>
+      <c r="E51" s="172"/>
+      <c r="F51" s="172"/>
       <c r="G51" s="66" t="s">
         <v>258</v>
       </c>
@@ -4845,17 +4845,17 @@
       <c r="A52" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="157" t="s">
+      <c r="B52" s="134" t="s">
         <v>185</v>
       </c>
-      <c r="C52" s="109"/>
-      <c r="D52" s="109"/>
-      <c r="E52" s="109"/>
-      <c r="F52" s="109"/>
-      <c r="G52" s="136"/>
-      <c r="H52" s="109"/>
-      <c r="I52" s="136"/>
-      <c r="J52" s="158"/>
+      <c r="C52" s="108"/>
+      <c r="D52" s="108"/>
+      <c r="E52" s="108"/>
+      <c r="F52" s="108"/>
+      <c r="G52" s="115"/>
+      <c r="H52" s="108"/>
+      <c r="I52" s="115"/>
+      <c r="J52" s="135"/>
     </row>
     <row r="53" spans="1:10" ht="16.5" customHeight="1">
       <c r="A53" s="18" t="s">
@@ -4867,19 +4867,19 @@
       <c r="C53" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D53" s="156" t="s">
+      <c r="D53" s="133" t="s">
         <v>108</v>
       </c>
-      <c r="E53" s="156" t="s">
+      <c r="E53" s="133" t="s">
         <v>108</v>
       </c>
-      <c r="F53" s="156" t="s">
+      <c r="F53" s="133" t="s">
         <v>108</v>
       </c>
       <c r="G53" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="H53" s="156" t="s">
+      <c r="H53" s="133" t="s">
         <v>108</v>
       </c>
       <c r="I53" s="36" t="s">
@@ -4897,13 +4897,13 @@
       <c r="C54" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="D54" s="144"/>
-      <c r="E54" s="144"/>
-      <c r="F54" s="144"/>
+      <c r="D54" s="112"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
       <c r="G54" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="H54" s="144"/>
+      <c r="H54" s="112"/>
       <c r="I54" s="36" t="s">
         <v>112</v>
       </c>
@@ -4918,16 +4918,16 @@
       <c r="B55" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="C55" s="99" t="s">
+      <c r="C55" s="165" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="99"/>
-      <c r="E55" s="99"/>
-      <c r="F55" s="99"/>
-      <c r="G55" s="99"/>
-      <c r="H55" s="100"/>
-      <c r="I55" s="99"/>
-      <c r="J55" s="101"/>
+      <c r="D55" s="165"/>
+      <c r="E55" s="165"/>
+      <c r="F55" s="165"/>
+      <c r="G55" s="165"/>
+      <c r="H55" s="166"/>
+      <c r="I55" s="165"/>
+      <c r="J55" s="167"/>
     </row>
     <row r="56" spans="1:10" ht="16.5" customHeight="1">
       <c r="A56" s="23">
@@ -5038,10 +5038,10 @@
       <c r="F59" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="G59" s="104" t="s">
+      <c r="G59" s="116" t="s">
         <v>281</v>
       </c>
-      <c r="H59" s="105"/>
+      <c r="H59" s="170"/>
       <c r="I59" s="29" t="s">
         <v>126</v>
       </c>
@@ -5053,25 +5053,25 @@
       <c r="A60" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="B60" s="115" t="s">
+      <c r="B60" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="C60" s="116"/>
+      <c r="C60" s="173"/>
       <c r="D60" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="E60" s="115" t="s">
+      <c r="E60" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="F60" s="109"/>
-      <c r="G60" s="115" t="s">
+      <c r="F60" s="108"/>
+      <c r="G60" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="H60" s="109"/>
-      <c r="I60" s="115" t="s">
+      <c r="H60" s="108"/>
+      <c r="I60" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="J60" s="109"/>
+      <c r="J60" s="108"/>
     </row>
     <row r="61" spans="1:10" ht="16.5">
       <c r="A61" s="18" t="s">
@@ -5173,63 +5173,63 @@
       <c r="A64" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B64" s="135" t="s">
+      <c r="B64" s="140" t="s">
         <v>311</v>
       </c>
-      <c r="C64" s="136"/>
-      <c r="D64" s="136"/>
-      <c r="E64" s="136"/>
-      <c r="F64" s="136"/>
-      <c r="G64" s="136"/>
-      <c r="H64" s="136"/>
-      <c r="I64" s="136"/>
-      <c r="J64" s="136"/>
+      <c r="C64" s="115"/>
+      <c r="D64" s="115"/>
+      <c r="E64" s="115"/>
+      <c r="F64" s="115"/>
+      <c r="G64" s="115"/>
+      <c r="H64" s="115"/>
+      <c r="I64" s="115"/>
+      <c r="J64" s="115"/>
     </row>
     <row r="65" spans="1:10" ht="18" customHeight="1">
       <c r="A65" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B65" s="118" t="s">
+      <c r="B65" s="107" t="s">
         <v>183</v>
       </c>
-      <c r="C65" s="109"/>
-      <c r="D65" s="109"/>
-      <c r="E65" s="109"/>
-      <c r="F65" s="109"/>
-      <c r="G65" s="109"/>
-      <c r="H65" s="109"/>
-      <c r="I65" s="109"/>
-      <c r="J65" s="110"/>
+      <c r="C65" s="108"/>
+      <c r="D65" s="108"/>
+      <c r="E65" s="108"/>
+      <c r="F65" s="108"/>
+      <c r="G65" s="108"/>
+      <c r="H65" s="108"/>
+      <c r="I65" s="108"/>
+      <c r="J65" s="109"/>
     </row>
     <row r="66" spans="1:10" ht="36" customHeight="1" thickBot="1">
-      <c r="A66" s="117" t="s">
+      <c r="A66" s="174" t="s">
         <v>134</v>
       </c>
-      <c r="B66" s="109"/>
-      <c r="C66" s="109"/>
-      <c r="D66" s="109"/>
-      <c r="E66" s="109"/>
-      <c r="F66" s="109"/>
-      <c r="G66" s="109"/>
-      <c r="H66" s="109"/>
-      <c r="I66" s="109"/>
-      <c r="J66" s="110"/>
+      <c r="B66" s="108"/>
+      <c r="C66" s="108"/>
+      <c r="D66" s="108"/>
+      <c r="E66" s="108"/>
+      <c r="F66" s="108"/>
+      <c r="G66" s="108"/>
+      <c r="H66" s="108"/>
+      <c r="I66" s="108"/>
+      <c r="J66" s="109"/>
     </row>
     <row r="67" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A67" s="5"/>
-      <c r="B67" s="111" t="s">
+      <c r="B67" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="C67" s="112"/>
-      <c r="D67" s="112"/>
-      <c r="E67" s="112"/>
-      <c r="F67" s="113"/>
-      <c r="G67" s="111" t="s">
+      <c r="C67" s="130"/>
+      <c r="D67" s="130"/>
+      <c r="E67" s="130"/>
+      <c r="F67" s="131"/>
+      <c r="G67" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="H67" s="112"/>
-      <c r="I67" s="112"/>
-      <c r="J67" s="114"/>
+      <c r="H67" s="130"/>
+      <c r="I67" s="130"/>
+      <c r="J67" s="132"/>
     </row>
     <row r="68" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A68" s="6" t="s">
@@ -5267,15 +5267,15 @@
       <c r="A69" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B69" s="108" t="s">
+      <c r="B69" s="136" t="s">
         <v>184</v>
       </c>
-      <c r="C69" s="109"/>
-      <c r="D69" s="109"/>
-      <c r="E69" s="109"/>
-      <c r="F69" s="109"/>
-      <c r="G69" s="109"/>
-      <c r="H69" s="110"/>
+      <c r="C69" s="108"/>
+      <c r="D69" s="108"/>
+      <c r="E69" s="108"/>
+      <c r="F69" s="108"/>
+      <c r="G69" s="108"/>
+      <c r="H69" s="109"/>
       <c r="I69" s="49"/>
       <c r="J69" s="49"/>
     </row>
@@ -5304,10 +5304,10 @@
       <c r="H70" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="I70" s="104" t="s">
+      <c r="I70" s="116" t="s">
         <v>138</v>
       </c>
-      <c r="J70" s="110"/>
+      <c r="J70" s="109"/>
     </row>
     <row r="71" spans="1:10" ht="16.5">
       <c r="A71" s="18" t="s">
@@ -5319,10 +5319,10 @@
       <c r="C71" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="D71" s="104" t="s">
+      <c r="D71" s="116" t="s">
         <v>93</v>
       </c>
-      <c r="E71" s="132"/>
+      <c r="E71" s="119"/>
       <c r="F71" s="83" t="s">
         <v>315</v>
       </c>
@@ -5337,19 +5337,19 @@
       <c r="A72" s="68" t="s">
         <v>139</v>
       </c>
-      <c r="B72" s="166" t="s">
+      <c r="B72" s="98" t="s">
         <v>314</v>
       </c>
-      <c r="C72" s="168" t="s">
+      <c r="C72" s="100" t="s">
         <v>314</v>
       </c>
-      <c r="D72" s="171" t="s">
+      <c r="D72" s="103" t="s">
         <v>315</v>
       </c>
-      <c r="E72" s="169" t="s">
+      <c r="E72" s="101" t="s">
         <v>315</v>
       </c>
-      <c r="F72" s="173" t="s">
+      <c r="F72" s="105" t="s">
         <v>314</v>
       </c>
       <c r="G72" s="84" t="s">
@@ -5358,20 +5358,20 @@
       <c r="H72" s="76" t="s">
         <v>314</v>
       </c>
-      <c r="I72" s="104" t="s">
+      <c r="I72" s="116" t="s">
         <v>140</v>
       </c>
-      <c r="J72" s="110"/>
+      <c r="J72" s="109"/>
     </row>
     <row r="73" spans="1:10" ht="16.5" customHeight="1">
       <c r="A73" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="B73" s="167"/>
-      <c r="C73" s="167"/>
-      <c r="D73" s="172"/>
-      <c r="E73" s="170"/>
-      <c r="F73" s="174"/>
+      <c r="B73" s="99"/>
+      <c r="C73" s="99"/>
+      <c r="D73" s="104"/>
+      <c r="E73" s="102"/>
+      <c r="F73" s="106"/>
       <c r="G73" s="82" t="s">
         <v>316</v>
       </c>
@@ -5385,17 +5385,17 @@
       <c r="A74" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B74" s="115" t="s">
+      <c r="B74" s="113" t="s">
         <v>144</v>
       </c>
-      <c r="C74" s="109"/>
-      <c r="D74" s="109"/>
-      <c r="E74" s="136"/>
-      <c r="F74" s="136"/>
-      <c r="G74" s="109"/>
-      <c r="H74" s="109"/>
-      <c r="I74" s="109"/>
-      <c r="J74" s="110"/>
+      <c r="C74" s="108"/>
+      <c r="D74" s="108"/>
+      <c r="E74" s="115"/>
+      <c r="F74" s="115"/>
+      <c r="G74" s="108"/>
+      <c r="H74" s="108"/>
+      <c r="I74" s="108"/>
+      <c r="J74" s="109"/>
     </row>
     <row r="75" spans="1:10" ht="16.5" customHeight="1">
       <c r="A75" s="18" t="s">
@@ -5422,10 +5422,10 @@
       <c r="H75" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="I75" s="141" t="s">
+      <c r="I75" s="110" t="s">
         <v>90</v>
       </c>
-      <c r="J75" s="141" t="s">
+      <c r="J75" s="110" t="s">
         <v>90</v>
       </c>
     </row>
@@ -5439,47 +5439,47 @@
       <c r="C76" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="D76" s="149" t="s">
+      <c r="D76" s="114" t="s">
         <v>149</v>
       </c>
-      <c r="E76" s="109"/>
-      <c r="F76" s="109"/>
-      <c r="G76" s="109"/>
-      <c r="H76" s="110"/>
-      <c r="I76" s="144"/>
-      <c r="J76" s="144"/>
+      <c r="E76" s="108"/>
+      <c r="F76" s="108"/>
+      <c r="G76" s="108"/>
+      <c r="H76" s="109"/>
+      <c r="I76" s="112"/>
+      <c r="J76" s="112"/>
     </row>
     <row r="77" spans="1:10" ht="16.5" customHeight="1">
       <c r="A77" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="B77" s="115" t="s">
+      <c r="B77" s="113" t="s">
         <v>151</v>
       </c>
-      <c r="C77" s="109"/>
-      <c r="D77" s="109"/>
-      <c r="E77" s="109"/>
-      <c r="F77" s="109"/>
-      <c r="G77" s="109"/>
-      <c r="H77" s="109"/>
-      <c r="I77" s="109"/>
-      <c r="J77" s="110"/>
+      <c r="C77" s="108"/>
+      <c r="D77" s="108"/>
+      <c r="E77" s="108"/>
+      <c r="F77" s="108"/>
+      <c r="G77" s="108"/>
+      <c r="H77" s="108"/>
+      <c r="I77" s="108"/>
+      <c r="J77" s="109"/>
     </row>
     <row r="78" spans="1:10" ht="16.5" customHeight="1">
       <c r="A78" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="B78" s="104" t="s">
+      <c r="B78" s="116" t="s">
         <v>152</v>
       </c>
-      <c r="C78" s="109"/>
-      <c r="D78" s="109"/>
-      <c r="E78" s="109"/>
-      <c r="F78" s="109"/>
-      <c r="G78" s="109"/>
-      <c r="H78" s="109"/>
-      <c r="I78" s="109"/>
-      <c r="J78" s="110"/>
+      <c r="C78" s="108"/>
+      <c r="D78" s="108"/>
+      <c r="E78" s="108"/>
+      <c r="F78" s="108"/>
+      <c r="G78" s="108"/>
+      <c r="H78" s="108"/>
+      <c r="I78" s="108"/>
+      <c r="J78" s="109"/>
     </row>
     <row r="79" spans="1:10" ht="16.5" customHeight="1">
       <c r="A79" s="18" t="s">
@@ -5521,21 +5521,21 @@
       <c r="H80" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="I80" s="162" t="s">
+      <c r="I80" s="117" t="s">
         <v>153</v>
       </c>
-      <c r="J80" s="110"/>
+      <c r="J80" s="109"/>
     </row>
     <row r="81" spans="1:10" ht="16.5" customHeight="1">
       <c r="A81" s="68" t="s">
         <v>312</v>
       </c>
-      <c r="B81" s="98" t="s">
+      <c r="B81" s="164" t="s">
         <v>297</v>
       </c>
-      <c r="C81" s="98"/>
-      <c r="D81" s="98"/>
-      <c r="E81" s="98"/>
+      <c r="C81" s="164"/>
+      <c r="D81" s="164"/>
+      <c r="E81" s="164"/>
       <c r="F81" s="51" t="s">
         <v>296</v>
       </c>
@@ -5650,17 +5650,17 @@
       <c r="A86" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B86" s="118" t="s">
+      <c r="B86" s="107" t="s">
         <v>162</v>
       </c>
-      <c r="C86" s="109"/>
-      <c r="D86" s="109"/>
-      <c r="E86" s="109"/>
-      <c r="F86" s="109"/>
-      <c r="G86" s="109"/>
-      <c r="H86" s="109"/>
-      <c r="I86" s="109"/>
-      <c r="J86" s="110"/>
+      <c r="C86" s="108"/>
+      <c r="D86" s="108"/>
+      <c r="E86" s="108"/>
+      <c r="F86" s="108"/>
+      <c r="G86" s="108"/>
+      <c r="H86" s="108"/>
+      <c r="I86" s="108"/>
+      <c r="J86" s="109"/>
     </row>
     <row r="87" spans="1:10" ht="16.5" customHeight="1">
       <c r="A87" s="1"/>
@@ -8794,11 +8794,66 @@
     <row r="1016" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="81">
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="C55:J55"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="G67:J67"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="B64:J64"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="J27:J29"/>
+    <mergeCell ref="I31:I33"/>
+    <mergeCell ref="J31:J33"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="B52:J52"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="B43:J43"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="C48:E48"/>
     <mergeCell ref="B86:J86"/>
     <mergeCell ref="I27:I29"/>
     <mergeCell ref="B77:J77"/>
@@ -8815,66 +8870,11 @@
     <mergeCell ref="A40:J40"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B38:J38"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="F53:F54"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="B52:J52"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="B43:J43"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B64:J64"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="B39:J39"/>
-    <mergeCell ref="J27:J29"/>
-    <mergeCell ref="I31:I33"/>
-    <mergeCell ref="J31:J33"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="C55:J55"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="G67:J67"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="F72:F73"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/2026 여름신앙학교 데일리 스케줄(최종).xlsx
+++ b/2026 여름신앙학교 데일리 스케줄(최종).xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\카카오톡 받은 파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDD8EE3-232F-4DEE-AEB4-65E09702F441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037A144D-DE27-4CB0-AD9E-31CC01D091E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="타임테이블" sheetId="1" r:id="rId1"/>
     <sheet name="교사 비상연락망" sheetId="2" r:id="rId2"/>
     <sheet name="학생 비상연락망" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'학생 비상연락망'!$A$1:$F$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1590,15 +1593,9 @@
     <t>010-4599-8022</t>
   </si>
   <si>
-    <t>0106434-9495</t>
-  </si>
-  <si>
     <t>010-6235-9486</t>
   </si>
   <si>
-    <t>0106434-9486</t>
-  </si>
-  <si>
     <t>010-9670-2075</t>
   </si>
   <si>
@@ -1681,6 +1678,14 @@
   </si>
   <si>
     <t>010-4203-2677</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-6434-9486</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-6434-9495</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3914,7 +3919,7 @@
         <v>26</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C16" s="24" t="s">
         <v>27</v>
@@ -3935,10 +3940,10 @@
         <v>19</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1">
@@ -8931,7 +8936,7 @@
         <v>326</v>
       </c>
       <c r="D3" s="89" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1">
@@ -9114,68 +9119,68 @@
       <c r="A4" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B4" s="92" t="s">
-        <v>359</v>
+      <c r="B4" s="90" t="s">
+        <v>362</v>
       </c>
       <c r="C4" s="90" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D4" s="90" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="E4" s="90" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F4" s="90" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B5" s="90" t="s">
-        <v>362</v>
+      <c r="B5" s="92" t="s">
+        <v>359</v>
       </c>
       <c r="C5" s="90" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D5" s="90" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="E5" s="90" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F5" s="90" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B6" s="93" t="s">
-        <v>364</v>
-      </c>
-      <c r="C6" s="93" t="s">
-        <v>365</v>
+      <c r="B6" s="90" t="s">
+        <v>371</v>
+      </c>
+      <c r="C6" s="90" t="s">
+        <v>372</v>
       </c>
       <c r="D6" s="90" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="E6" s="90" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F6" s="90" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B7" s="94" t="s">
-        <v>366</v>
+      <c r="B7" s="90" t="s">
+        <v>393</v>
       </c>
       <c r="C7" s="90" t="s">
         <v>367</v>
@@ -9183,11 +9188,11 @@
       <c r="D7" s="90" t="s">
         <v>355</v>
       </c>
-      <c r="E7" s="90" t="s">
-        <v>406</v>
-      </c>
-      <c r="F7" s="90" t="s">
-        <v>407</v>
+      <c r="E7" s="95" t="s">
+        <v>428</v>
+      </c>
+      <c r="F7" s="95" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9204,90 +9209,90 @@
         <v>355</v>
       </c>
       <c r="E8" s="90" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="F8" s="90" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B9" s="93" t="s">
-        <v>369</v>
-      </c>
-      <c r="C9" s="93" t="s">
-        <v>370</v>
+      <c r="B9" s="94" t="s">
+        <v>366</v>
+      </c>
+      <c r="C9" s="90" t="s">
+        <v>367</v>
       </c>
       <c r="D9" s="90" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="E9" s="90" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="F9" s="90" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="B10" s="90" t="s">
-        <v>371</v>
-      </c>
-      <c r="C10" s="90" t="s">
-        <v>372</v>
+      <c r="B10" s="93" t="s">
+        <v>369</v>
+      </c>
+      <c r="C10" s="93" t="s">
+        <v>370</v>
       </c>
       <c r="D10" s="90" t="s">
         <v>361</v>
       </c>
       <c r="E10" s="90" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="F10" s="90" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="90" t="s">
-        <v>374</v>
-      </c>
-      <c r="B11" s="92" t="s">
-        <v>375</v>
-      </c>
-      <c r="C11" s="90" t="s">
-        <v>376</v>
+        <v>358</v>
+      </c>
+      <c r="B11" s="93" t="s">
+        <v>364</v>
+      </c>
+      <c r="C11" s="93" t="s">
+        <v>365</v>
       </c>
       <c r="D11" s="90" t="s">
         <v>355</v>
       </c>
       <c r="E11" s="90" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="F11" s="90" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="90" t="s">
         <v>374</v>
       </c>
-      <c r="B12" s="90" t="s">
-        <v>377</v>
+      <c r="B12" s="92" t="s">
+        <v>375</v>
       </c>
       <c r="C12" s="90" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D12" s="90" t="s">
         <v>355</v>
       </c>
       <c r="E12" s="90" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F12" s="90" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -9304,10 +9309,10 @@
         <v>361</v>
       </c>
       <c r="E13" s="90" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F13" s="90" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -9324,30 +9329,30 @@
         <v>355</v>
       </c>
       <c r="E14" s="90" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F14" s="90" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="90" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="B15" s="90" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C15" s="90" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="D15" s="90" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="E15" s="90" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="F15" s="90" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -9355,19 +9360,19 @@
         <v>383</v>
       </c>
       <c r="B16" s="90" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C16" s="90" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D16" s="90" t="s">
         <v>361</v>
       </c>
       <c r="E16" s="90" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F16" s="90" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -9375,10 +9380,10 @@
         <v>383</v>
       </c>
       <c r="B17" s="90" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C17" s="90" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D17" s="90" t="s">
         <v>361</v>
@@ -9395,19 +9400,19 @@
         <v>383</v>
       </c>
       <c r="B18" s="90" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C18" s="90" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="D18" s="90" t="s">
         <v>361</v>
       </c>
       <c r="E18" s="90" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F18" s="90" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -9415,19 +9420,19 @@
         <v>383</v>
       </c>
       <c r="B19" s="90" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C19" s="90" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="D19" s="90" t="s">
         <v>361</v>
       </c>
       <c r="E19" s="90" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="F19" s="90" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -9444,7 +9449,7 @@
         <v>361</v>
       </c>
       <c r="E20" s="90" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F20" s="90" t="s">
         <v>399</v>
@@ -9452,25 +9457,30 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="90" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="B21" s="90" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C21" s="90" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D21" s="90" t="s">
-        <v>355</v>
-      </c>
-      <c r="E21" s="95" t="s">
-        <v>430</v>
-      </c>
-      <c r="F21" s="95" t="s">
-        <v>431</v>
+        <v>361</v>
+      </c>
+      <c r="E21" s="90" t="s">
+        <v>419</v>
+      </c>
+      <c r="F21" s="90" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1" xr:uid="{B90C2390-EDF1-4364-8397-ED53C979A520}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
